--- a/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
+++ b/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
@@ -9179,7 +9179,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở bài “Bảng cộng qua 10”, GV chiếu bảng cộng trên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Bảng cộng qua 10”, GV chiếu bảng cộng trên màn hình rồi bấm hiện dần từng dòng theo thứ tự HS nêu; nhìn bảng lớn
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở trò chơi luyện bảng cộng có tự chấm: mỗi em trả lời rồi nhìn máy báo đúng, sai ngay để biết phép nào mình còn chậm
 KNS: KN chi tiêu hợp lí: tính toán khi mua bán, biết tiết kiệm.</t>
         </is>
       </c>
@@ -9515,7 +9516,8 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở bài “Bảng trừ qua 10”, GV chiếu bảng trừ trên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Bảng trừ qua 10”, GV chiếu bảng trừ trên màn hình rồi bấm hiện dần từng dòng theo thứ tự HS nêu; nhìn bảng lớn
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV mở trò chơi luyện bảng trừ có tự chấm: mỗi em trả lời rồi nhìn máy báo đúng, sai ngay để biết phép nào mình còn chậm
 KNS: KN chi tiêu hợp lí: tính toán khi mua bán, biết tiết kiệm.</t>
         </is>
       </c>
@@ -10092,7 +10094,12 @@
           <t>50</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài cộng có nhớ số có hai chữ số với số có hai chữ số, GV mở bài tập tương tác đặt tính rồi tính; sau mỗi câu máy báo đúng
+Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to bài toán có lời văn, gạch chân số liệu và từ khoá tất cả, cả hai; HS đọc kĩ đề rồi mới chọn phép tính</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -10394,7 +10401,12 @@
           <t>60</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 1): Ở bài trừ có nhớ số có hai chữ số cho số có hai chữ số, GV mở bài tập tương tác đặt tính rồi tính; sau mỗi câu máy báo đúng
+Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to bài toán có lời văn, gạch chân số liệu và từ khoá còn lại, ít hơn; HS đọc kĩ đề rồi mới chọn phép tính</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -12126,7 +12138,12 @@
           <t>114</t>
         </is>
       </c>
-      <c r="H117" s="4" t="inlineStr"/>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu mô hình ba chiều khối trụ, khối cầu trên máy, xoay đủ mọi phía và bổ đôi khối để HS nhìn thấy mặt cắt
+Năng lực số Miền 3 (Cơ bản, bậc 1): HS xếp công trình từ các khối, GV chụp ảnh từng công trình rồi ghép thành bức tranh thành phố hình học của lớp chiếu lên màn hình</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -12152,7 +12169,12 @@
           <t>115</t>
         </is>
       </c>
-      <c r="H118" s="4" t="inlineStr"/>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu mô hình ba chiều khối trụ, khối cầu trên máy, xoay đủ mọi phía và bổ đôi khối để HS nhìn thấy mặt cắt
+Năng lực số Miền 3 (Cơ bản, bậc 1): HS xếp công trình từ các khối, GV chụp ảnh từng công trình rồi ghép thành bức tranh thành phố hình học của lớp chiếu lên màn hình</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -13081,7 +13103,12 @@
           <t>144</t>
         </is>
       </c>
-      <c r="H147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá bài “Phép trừ không nhớ trong phạm vi 1 000”, GV chiếu phép trừ đặt tính dọc lên màn hình và cho hiện dần từng hàng đơn vị, chục
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS đặt tính và tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -13480,7 +13507,12 @@
           <t>157</t>
         </is>
       </c>
-      <c r="H160" s="4" t="inlineStr"/>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV cùng HS kiểm đếm số liệu thật của lớp (số bạn thích mỗi loại quả, số bạn đi bộ - đi xe đạp - đi ô tô) rồi nhập ngay vào bảng trên…
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV sửa thử một số liệu trong bảng, biểu đồ tranh trên màn hình đổi theo ngay; HS nhận ra biểu đồ vẽ đúng hay sai là do số liệu nhập vào</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -17977,7 +18009,9 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở chủ đề “Em yêu làn điệu dân ca”, GV mở bản thu bài Con chim chích choè và một hai làn điệu dân ca quen thuộc cho HS nghe đoán tên bài
+Năng lực số Miền 3 (Cơ bản, bậc 1): Sau khi các nhóm biểu diễn, GV quay lại tiết mục rồi chiếu cho cả lớp cùng xem; mỗi nhóm nhìn phần trình diễn của mình để nói chỗ hát đã đều
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -18209,7 +18243,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá – Luyện tập chủ đề “Tuổi thơ”, GV chiếu hình tiết tấu phóng to lên màn hình và mở bản gõ mẫu từ học liệu số
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Vận dụng – Sáng tạo, GV dùng điện thoại ghi âm phần hoà tấu của từng nhóm với thanh phách, song loan, trống con rồi mở lại cho cả lớp nghe</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -18570,7 +18609,9 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở phần Khởi động chủ đề “Gia đình yêu thương”, GV mở lần lượt các đoạn giai điệu đã học từ học liệu số cho HS nghe đoán tên bài
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở phần Biểu diễn, GV ghi âm phần hát kết hợp gõ đệm của từng tổ rồi mở lại cho cả lớp nghe
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -19108,7 +19149,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở chủ đề “Sự kết hợp của các hình cơ bản”, GV chiếu ảnh các đồ vật quen thuộc rồi bấm tách dần thành hình tròn, vuông, tam giác, chữ nhật ghép lại
+Năng lực số Miền 3 (Cơ bản, bậc 1): Làm xong sản phẩm ba chiều, GV chụp ảnh từ hai phía rồi chiếu lên màn hình thành bộ sưu tập của lớp</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -19292,7 +19338,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở chủ đề “Sự kết hợp thú vị của khối”, GV chiếu ảnh đồ vật ba chiều rồi bấm tách dần thành các khối lập phương, khối hộp, khối trụ, khối cầu
+Năng lực số Miền 3 (Cơ bản, bậc 1): Sắp xếp xong, GV chụp ảnh sản phẩm của từng nhóm từ hai phía rồi chiếu lên màn hình; HS nhìn sản phẩm ở góc khác nên phát hiện chỗ đặt chưa cân</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -19382,7 +19433,12 @@
           <t>14</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở chủ đề “Sắc màu thiên nhiên”, GV chiếu ảnh phong cảnh bốn mùa và phóng to từng mảng màu trời, cây, nước; HS gọi tên màu, nói màu nào làm bức tranh ấm
+Năng lực số Miền 3 (Cơ bản, bậc 1): Vẽ xong, GV chụp ảnh tranh của cả lớp rồi chiếu thành phòng tranh trên màn hình; mỗi em giới thiệu bức của mình</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -19408,7 +19464,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá kĩ thuật in của chủ đề “Sắc màu thiên nhiên”, GV chiếu ảnh chụp gần mặt sau chiếc lá bàng, lát thân chuối
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Luyện tập – Sáng tạo, GV dùng điện thoại chụp sản phẩm in của các nhóm rồi chiếu lên màn hình thành một bộ sưu tập nhỏ, cả lớp cùng xem</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -19434,7 +19495,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá kết hợp chất liệu của chủ đề “Sắc màu thiên nhiên”, GV chiếu ảnh chụp gần các sản phẩm mẫu: khung ảnh dán lá khô, hộp bọc giấy màu
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Trưng bày, GV chụp sản phẩm của các nhóm rồi chiếu thành một bộ sưu tập nhỏ trên màn hình; cả lớp cùng xem</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -19528,7 +19594,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chân dung 3D của chủ đề “Gương mặt thân quen”, GV chiếu ảnh chụp hai sản phẩm mẫu từ nhiều phía
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Trưng bày, GV chụp sản phẩm của các nhóm từ hai góc rồi chiếu lên màn hình; cả lớp cùng xem</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -19554,7 +19625,12 @@
           <t>20</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá đắp nổi chân dung của chủ đề “Gương mặt thân quen”, GV chiếu ảnh chụp nghiêng hai sản phẩm cùng một gương mặt
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Trưng bày, GV chụp sản phẩm đắp nổi của các nhóm từ hai góc sáng khác nhau rồi chiếu lên</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -19644,7 +19720,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “Bữa cơm gia đình”, GV chiếu ảnh chụp mâm cơm nhìn từ trên xuống và nhìn ngang, phóng to cách xếp bát đũa, món ăn
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Trưng bày, GV chụp sản phẩm mâm cơm ba chiều của các nhóm rồi chiếu lên màn hình; cả lớp cùng xem, chọn mâm cơm sắp gọn</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -19670,7 +19751,12 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khởi động chủ đề “Bữa cơm gia đình”, GV chiếu ảnh chụp một lọ hoa đã trang trí bên cạnh vỏ chai chưa trang trí
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Trưng bày, GV chụp lọ hoa của các nhóm rồi chiếu lên màn hình thành một bộ sưu tập nhỏ; cả lớp cùng xem</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -19761,7 +19847,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Khám phá chủ đề “Thầy cô của em”, GV chiếu ảnh chụp các hoạt động của thầy cô ở trường: đang giảng bài, đang chấm vở, đang chơi cùng học sinh
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Trưng bày, GV chụp bài của các nhóm rồi chiếu lên màn hình; cả lớp cùng xem, chọn bài thể hiện rõ hoạt động của thầy cô và nói bạn đã…</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -19911,7 +20002,12 @@
           <t>32</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Thảo luận chủ đề “Đồ chơi từ tạo hình con vật”, GV chiếu ảnh hộp bút lộn xộn bên cạnh ảnh ống đựng bút gọn gàng
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Trưng bày, GV chụp ống đựng bút của các nhóm rồi chiếu lên màn hình thành bộ sưu tập; cả lớp cùng xem, chọn sản phẩm chắc chắn</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">

--- a/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
+++ b/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
@@ -655,7 +655,9 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động đọc văn bản bài “Ngày hôm qua đâu rồi?”, GV chiếu tranh tờ lịch và mở bản đọc mẫu bài thơ trên tivi
+Năng lực số Miền 5 (Cơ bản, bậc 1): Ở phần đọc hiểu, khi liên hệ về quý trọng thời gian, GV mở bài tập tương tác trên tivi có các tranh việc học, việc nhà, vui chơi, nghỉ ngơi
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1051,8 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu phóng to tranh minh hoạ bài đọc “Em có xinh không?”.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh minh hoạ bài đọc “Em có xinh không?” và mở bản đọc mẫu để HS vừa nhìn tranh vừa nghe giọng đọc lời voi anh, voi em
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm một, hai lượt HS đọc lời nhân vật rồi mở lại cho cả lớp nghe; các em tự nhận ra chỗ đọc chưa rõ lời thoại
 KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
@@ -1140,7 +1143,9 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh minh hoạ bài đọc “Một giờ học” và mở bản đọc mẫu lời thầy giáo, lời bạn Quang
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc phân vai của một nhóm rồi mở lại cho cả lớp nghe; các em nhận ra giọng thầy giáo phải chậm và ấm, giọng Quang lúc đầu ngập ngừng
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1386,9 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Cầu thủ dự bị”, GV chiếu tranh minh hoạ phóng to và một đoạn phim ngắn về trận bóng của thiếu nhi để HS gọi tên môn thể thao
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc phân vai của một nhóm rồi mở lại cho cả lớp nghe; các em nhận ra chỗ nào là lời người kể, chỗ nào là lời nhân vật
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1539,8 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Vào chủ điểm mới với bài đọc “Cô giáo lớp em”, GV chiếu tranh minh hoạ phóng to.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Vào chủ điểm mới với bài đọc “Cô giáo lớp em”, GV chiếu tranh minh hoạ phóng to và mở bản đọc mẫu bài thơ
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc thuộc lòng một khổ thơ của vài HS rồi mở lại cho cả lớp nghe; các em nhận ra chỗ ngắt nhịp chưa đúng, chỗ đọc còn nhỏ
 QTE: QTE: liên hệ quyền được học tập, vui chơi và được yêu thương của trẻ em qua nhân vật, chi tiết trong bài đọc.</t>
         </is>
       </c>
@@ -1779,7 +1787,8 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ghi âm lượt đọc thuộc một khổ thơ của vài.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Cái trống trường em”, GV mở đoạn ghi âm tiếng trống trường và chiếu ảnh chiếc trống ở sân trường mình; HS nói tiếng trống báo hiệu điều gì
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc thuộc một khổ thơ của vài HS rồi mở lại cho cả lớp nghe; các em nhận ra chỗ ngắt nhịp chưa đúng
 KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
@@ -2022,7 +2031,8 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Trước bài đọc “Yêu lắm trường ơi!”, GV chiếu ảnh chính ngôi trường mình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Yêu lắm trường ơi!”, GV chiếu ảnh chính ngôi trường mình: cổng trường, sân chơi, lớp học, thư viện
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc thuộc một khổ thơ của vài HS rồi mở lại cho cả lớp nghe; các em nhận ra chỗ ngắt nhịp chưa đúng
 KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
@@ -2113,7 +2123,9 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Em học vẽ”, GV chiếu vài bức tranh thiếu nhi vẽ cảnh vật, con vật và phóng to từng mảng màu; HS gọi tên hình ảnh trong tranh
+Năng lực số Miền 3 (Cơ bản, bậc 1): Sau khi đọc, HS vẽ lại một hình ảnh mình thích trong bài; GV chụp ảnh các bài vẽ rồi chiếu thành phòng tranh của lớp để mỗi em giới thiệu tranh và nói…
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2370,9 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Khi trang sách mở ra”, GV chiếu bìa một số cuốn sách thiếu nhi quen thuộc và ảnh góc thư viện của trường
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc thuộc một khổ thơ của vài HS rồi mở lại cho cả lớp nghe; các em nhận ra chỗ ngắt nhịp chưa đúng
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2769,9 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Tớ nhớ cậu”, GV chiếu tranh minh hoạ phóng to và mở bản đọc mẫu; HS vừa nghe vừa nhìn tranh để nhận ra hai người bạn xa nhau đã làm…
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc phân vai của một nhóm rồi mở lại cho cả lớp nghe; các em nhận ra chỗ nào là lời người kể
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2922,8 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ghi âm lượt đọc phân vai của một nhóm.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Chữ A và những người bạn”, GV chiếu bảng chữ cái phóng to và tranh minh hoạ bài đọc; HS gọi tên các chữ cái thấy trong tranh
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc phân vai của một nhóm rồi mở lại cho cả lớp nghe; các em nhận ra chỗ nào là lời người kể
 KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
@@ -2998,7 +3015,9 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Nhím nâu kết bạn”, GV chiếu tranh minh hoạ phóng to và ảnh thật con nhím; HS nói đặc điểm bộ lông nhím
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc của vài HS rồi mở lại cho cả lớp nghe; các em nhận ra chỗ đọc còn nhỏ
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3661,9 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Em mang về yêu thương”, GV chiếu tranh khởi động phóng to và vài ảnh gia đình đón em bé mới sinh; HS nói mọi người trong tranh đang làm gì
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc thuộc một khổ thơ của vài HS rồi mở lại cho cả lớp nghe; các em nhận ra chỗ ngắt nhịp chưa đúng
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3784,8 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở hoạt động Đọc hiểu, GV chiếu sơ đồ còn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Đọc văn bản bài thơ “Mẹ”, GV chiếu tranh minh hoạ phóng to lên màn hình và mở bản đọc mẫu giọng nhẹ nhàng
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở hoạt động Đọc hiểu, GV chiếu sơ đồ còn để trống những việc mẹ đã làm cho con; các nhóm đôi trao đổi rồi lên điền vào sơ đồ trên màn hình
 KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
@@ -3854,7 +3876,9 @@
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Đọc văn bản bài “Trò chơi của bố”, GV chiếu tranh minh hoạ phóng to và mở bản đọc mẫu có phân biệt lời bố với lời Hường
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Luyện đọc lại, GV dùng điện thoại ghi âm phần đọc phân vai của vài nhóm rồi mở cho cả lớp nghe
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4280,8 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 1): Ở hoạt động Đọc hiểu, GV chiếu sơ đồ còn trống về việc Ê-đi-xơn đã làm.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Đọc văn bản bài “Ánh sáng của yêu thương”, GV chiếu ảnh nhà bác học Ê-đi-xơn và chiếc đèn điện đầu tiên lên màn hình, đồng thời mở bản đọc mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 1): Ở hoạt động Đọc hiểu, GV chiếu sơ đồ còn trống về việc Ê-đi-xơn đã làm để cứu mẹ; các nhóm đôi trao đổi rồi lên điền vào sơ đồ chung
 KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
@@ -4347,7 +4372,9 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở hoạt động Đọc văn bản bài “Chơi chong chóng”, GV chiếu tranh minh hoạ phóng to và mở bản đọc mẫu có phân biệt lời các nhân vật
+Năng lực số Miền 3 (Cơ bản, bậc 1): Ở hoạt động Luyện đọc lại, GV ghi âm phần đọc phân vai của vài nhóm rồi mở cho cả lớp nghe
+KNS: KN tự học: chọn sách phù hợp, kiên trì đọc và rút ra điều bổ ích cho bản thân.</t>
         </is>
       </c>
     </row>
@@ -5374,7 +5401,12 @@
           <t>210</t>
         </is>
       </c>
-      <c r="H161" s="4" t="inlineStr"/>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh minh hoạ bài đọc “Một giờ học” và mở bản đọc mẫu lời thầy giáo, lời bạn Quang
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc phân vai của một nhóm rồi mở lại cho cả lớp nghe; các em nhận ra giọng thầy giáo phải chậm và ấm, giọng Quang lúc đầu ngập ngừng</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -5623,7 +5655,12 @@
           <t>220</t>
         </is>
       </c>
-      <c r="H169" s="4" t="inlineStr"/>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Cầu thủ dự bị”, GV chiếu tranh minh hoạ phóng to và một đoạn phim ngắn về trận bóng của thiếu nhi để HS gọi tên môn thể thao
+Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc phân vai của một nhóm rồi mở lại cho cả lớp nghe; các em nhận ra chỗ nào là lời người kể, chỗ nào là lời nhân vật</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -14586,7 +14623,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 1): Chiếu các cách ứng xử trên màn hình cho HS chọn cách đúng gồm nhận lỗi, xin lỗi, sửa lỗi.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Ở bài “Nhận lỗi và sửa lỗi”, GV chiếu các đoạn phim tình huống ngắn về bạn nhỏ làm hỏng đồ của bạn, quên làm bài, nói dối mẹ
+Năng lực số Miền 5 (Cơ bản, bậc 1): GV chiếu các cách ứng xử trên màn hình cho HS chọn cách đúng gồm nhận lỗi, xin lỗi, sửa lỗi; máy báo đúng
 KNS: KN tự nhận thức: dám nhận lỗi và sửa lỗi; chịu trách nhiệm về việc mình làm.</t>
         </is>
       </c>

--- a/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
+++ b/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
@@ -773,8 +773,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI 2.A1.2: HS nhận biết công cụ AI có thể hỗ trợ gợi ý từ ngữ hoặc dàn ý khi viết đoạn văn tả đồ vật, nhưng chỉ dùng để tham khảo; HS tự viết bằng lời của mình, không sao chép nguyên văn và không nhập thông tin riêng tư.
-Năng lực số 1.1 CB1b: HS nhìn hình vật được quay trực tiếp trên màn hình và nêu được các chi tiết về màu sắc, hình dáng, chất liệu.</t>
+          <t>Năng lực số 1.1 CB1a: HS chọn bài đọc về thiếu nhi trong kho sách điện tử GV mở sẵn và nói vì sao chọn bài đó.</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1260,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1a: HS biết tìm kiếm nội dung đơn giản trong môi trường số; biết tìm đọc câu chuyện về thiên nhiên trên nguồn học liệu số do GV/cha mẹ cung cấp, chọn nội dung phù hợp và không bấm vào liên kết lạ.</t>
+          <t>Năng lực số 1.1 CB1a: HS xác định được nhu cầu thông tin và thực hiện tìm kiếm đơn giản trong môi trường số dưới sự hướng dẫn; biết tìm bài thơ/câu chuyện thiếu nhi phù hợp, chọn nguồn đọc an toàn, rõ tên bài, tác giả hoặc địa chỉ nguồn.</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1504,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1a: HS biết tìm kiếm nội dung đơn giản trong môi trường số; biết tìm đọc bài thơ về vẻ đẹp thiên nhiên trên nguồn học liệu số do GV/cha mẹ cung cấp, chọn nội dung phù hợp và không bấm vào liên kết lạ.</t>
+          <t>Năng lực số 1.2 CB1a: HS biết chọn nguồn thông tin số đơn giản, tin cậy và tôn trọng bản quyền khi tìm bài viết/hình ảnh về hoạt động thể thao; không tự ý tải hình ảnh lạ, không sao chép tùy tiện và biết ghi nhớ tên bài, nguồn đọc.</t>
         </is>
       </c>
     </row>
@@ -1752,8 +1751,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI 2.C3.1: HS nhận biết AI có thể hỗ trợ nhận diện hoặc phân loại con vật qua hình ảnh nhưng có thể nhầm; HS cần quan sát đặc điểm và kiểm tra lại với nguồn tin đáng tin cậy.
-Năng lực số 1.1 CB1a: HS biết tìm kiếm nội dung đơn giản về động vật hoang dã trên nguồn học liệu an toàn; biết ghi tên loài vật, thức ăn, nơi sống theo sơ đồ gợi ý.</t>
+          <t>Năng lực số 2.2 CB1a: HS nêu được điểm giống nhau giữa tấm thiệp, lời cảm ơn viết trên giấy và tin nhắn gửi bằng điện thoại.</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2239,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.2 CB1a: HS nêu được điểm giống nhau giữa tấm thiệp, lời cảm ơn viết trên giấy và tin nhắn gửi bằng điện thoại.</t>
+          <t>Năng lực số 3.1 CB1a: HS đọc bài viết được chiếu trên màn hình, nói được một câu kể rõ việc của bạn và một chỗ cần bổ sung.</t>
         </is>
       </c>
     </row>
@@ -2488,8 +2486,7 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI 2.A1.2: HS nhận biết AI có thể gợi ý dàn ý/từ ngữ khi viết đoạn văn bảo vệ môi trường, nhưng chỉ dùng tham khảo; HS phải tự viết bằng trải nghiệm thật và không nhập thông tin riêng tư.
-Năng lực số 3.1 CB1a: HS đọc bài viết được chiếu trên màn hình, nói được một câu kể rõ việc của bạn và một chỗ cần bổ sung.</t>
+          <t>Năng lực số 1.1 CB1b: HS quan sát ảnh phóng to và nêu được chi tiết mình sẽ đưa vào bài tả.</t>
         </is>
       </c>
     </row>
@@ -5403,8 +5400,7 @@
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): GV chiếu phóng to tranh minh hoạ bài đọc “Một giờ học” và mở bản đọc mẫu lời thầy giáo, lời bạn Quang
-Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc phân vai của một nhóm rồi mở lại cho cả lớp nghe; các em nhận ra giọng thầy giáo phải chậm và ấm, giọng Quang lúc đầu ngập ngừng</t>
+          <t>Năng lực số 1.1 CB1a: HS xác định được nhu cầu thông tin và thực hiện tìm kiếm đơn giản trong môi trường số dưới sự hướng dẫn; biết tìm bài thơ/câu chuyện thiếu nhi phù hợp, chọn nguồn đọc an toàn, rõ tên bài, tác giả hoặc địa chỉ nguồn.</t>
         </is>
       </c>
     </row>
@@ -5657,8 +5653,7 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 1): Trước bài đọc “Cầu thủ dự bị”, GV chiếu tranh minh hoạ phóng to và một đoạn phim ngắn về trận bóng của thiếu nhi để HS gọi tên môn thể thao
-Năng lực số Miền 2 (Cơ bản, bậc 1): GV ghi âm lượt đọc phân vai của một nhóm rồi mở lại cho cả lớp nghe; các em nhận ra chỗ nào là lời người kể, chỗ nào là lời nhân vật</t>
+          <t>Năng lực số 1.2 CB1a: HS biết chọn nguồn thông tin số đơn giản, tin cậy và tôn trọng bản quyền khi tìm bài viết/hình ảnh về hoạt động thể thao; không tự ý tải hình ảnh lạ, không sao chép tùy tiện và biết ghi nhớ tên bài, nguồn đọc.</t>
         </is>
       </c>
     </row>
@@ -7108,8 +7103,8 @@
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI 2.A1.2: HS biết AI có thể gợi ý câu/đoạn văn, nhưng phải tin tưởng ở mức hợp lí, kiểm tra lại và tự viết bằng trải nghiệm thật của mình.
-Năng lực số 1.1 CB1b: HS nhìn đoạn văn mẫu được tô màu và nêu được đoạn văn kể việc gồm mấy phần.</t>
+          <t>Tích hợp năng lực số/an toàn thiết bị: Biết đọc một số thông tin đơn giản trên bản hướng dẫn sử dụng; nhận biết cần hỏi người lớn trước khi dùng thiết bị điện, thiết bị số.
+Tích hợp AI - YCCĐ 2.A3.2: Biết công cụ AI có thể gợi ý thông tin nhưng cần người lớn hướng dẫn, kiểm tra; không tự làm theo hướng dẫn nguy hiểm hoặc chia sẻ thông tin riêng tư.</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7347,7 @@
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1b: HS nói ý theo từng ô của sơ đồ để GV gõ vào, rồi dựa vào dàn ý trên màn hình mà viết đoạn văn của mình.</t>
+          <t>Năng lực số 2.2 CB1a: HS nêu được vì sao phải kiểm tra tên người nhận trước khi gửi và vì sao mình cần nhờ bố mẹ gửi giúp.</t>
         </is>
       </c>
     </row>
@@ -7842,8 +7837,7 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI 2.A1.1: HS biết công cụ AI có thể gợi ý từ ngữ/câu văn, nhưng HS phải tự viết bằng trải nghiệm thật của mình và không nhập thông tin riêng tư của người thân.
-Năng lực số 2.2 CB1a: HS nêu được điểm giống nhau giữa đoạn văn viết trong vở và lời yêu thương gửi qua tin nhắn, tấm thiệp.</t>
+          <t>Năng lực số 1.1 CB1b: HS quan sát ảnh phóng to và nêu được chi tiết mình sẽ đưa vào bài tả.</t>
         </is>
       </c>
     </row>
@@ -8087,7 +8081,7 @@
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát GV tìm sách theo chủ đề trên máy và nêu được tên một cuốn sách mình muốn đọc.</t>
+          <t>Năng lực số 5.2 CB1b: HS nói ý theo từng ô của sơ đồ để GV gõ vào, rồi dựa vào dàn ý trên màn hình mà viết đoạn văn của mình.</t>
         </is>
       </c>
     </row>
@@ -20394,8 +20388,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS chỉ được trên sơ đồ đường di chuyển của tổ mình trong “Chuyển đội hình hàng ngang thành đội hình vòng tròn và ngược lại”.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20422,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS chỉ được trên sơ đồ đường di chuyển của tổ mình trong “Chuyển đội hình hàng dọc thành đội hình vòng tròn và ngược lại”.
+          <t>Năng lực số 1.1 CB1b: HS chỉ được trên sơ đồ đường di chuyển của tổ mình trong “Chuyển đội hình hàng ngang thành đội hình vòng tròn và ngược lại”.
 KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
@@ -20498,8 +20491,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Giậm chân tại chỗ, đứng lại” đã chọn sẵn, cho chạy chậm.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -20704,8 +20696,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1b: HS tập “Động tác vươn thở, động tác tay” đúng theo nhịp phát ra và tự nhận ra khi mình lệch nhịp.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -20963,11 +20954,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc được bảng theo dõi phần đội hình đội ngũ và một số động tác bài thể dục và nói được mình tiến bộ ở nội dung nào.</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -21034,8 +21021,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Bài tập phối hợp di chuyển vòng trái, vòng phải” đã chọn sẵn, cho chạy chậm.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -21103,8 +21089,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Bài tập phối hợp di chuyển nhanh dần theo vạch kẻ thẳng” mà mình hay làm sai.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -21241,8 +21226,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Các động tác quỳ, ngồi cơ bản” đã chọn sẵn, cho chạy chậm.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -21580,8 +21564,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS xem lại clip mình thực hiện “Động tác di chuyển không bóng” cho chạy chậm và chỉ ra được chỗ mình làm chưa đúng.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -21684,8 +21667,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1b: HS tập “Động tác di chuyển không bóng” đúng theo nhịp phát ra và tự nhận ra khi mình lệch nhịp.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -21754,8 +21736,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở phần Hình thành kiến thức bài “Động tác dẫn bóng” của chủ đề Bóng rổ, GV chiếu trên tivi video mẫu.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -21789,8 +21770,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Động tác dẫn bóng” mà mình hay làm sai.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -22048,11 +22028,7 @@
           <t>54</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Động tác tung và bắt bóng bằng hai tay” đã chọn sẵn, cho chạy chậm.</t>
-        </is>
-      </c>
+      <c r="H57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -22116,11 +22092,7 @@
           <t>56</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc được bảng theo dõi phần kĩ năng vận động với bóng (thể thao tự chọn) và nói được mình tiến bộ ở nội dung nào.</t>
-        </is>
-      </c>
+      <c r="H59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -22150,11 +22122,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc được bảng theo dõi phần kĩ năng vận động với bóng (thể thao tự chọn) và nói được mình tiến bộ ở nội dung nào.</t>
-        </is>
-      </c>
+      <c r="H60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -22312,11 +22280,7 @@
           <t>62</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Động tác ném rổ bằng hai tay trước ngực” đã chọn sẵn, cho chạy chậm.</t>
-        </is>
-      </c>
+      <c r="H65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -22534,11 +22498,7 @@
           <t>69</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB1b: HS chọn và ghi được hai việc rèn luyện ở nhà gắn với các nội dung đã học trong năm.</t>
-        </is>
-      </c>
+      <c r="H72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">

--- a/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
+++ b/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
@@ -741,11 +741,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1a: HS chọn bài đọc về thiếu nhi trong kho sách điện tử GV mở sẵn và nói vì sao chọn bài đó.</t>
-        </is>
-      </c>
+      <c r="H10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1013,12 +1009,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1a: HS biết tìm kiếm nội dung đơn giản trong môi trường số; biết tìm đọc bài thơ, câu chuyện về ngày Tết trên nguồn học liệu số do GV cung cấp, chọn nội dung phù hợp và không bấm vào liên kết lạ.
-Tích hợp AI 2.A1.2: HS nhận biết công cụ AI như ChatGPT/Gemini có thể gợi ý lời chúc Tết hoặc sửa lỗi chính tả; HS chỉ dùng để tham khảo, tự viết bằng lời chân thành, không sao chép nguyên văn và không nhập thông tin riêng tư.</t>
-        </is>
-      </c>
+      <c r="H19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1228,11 +1219,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1a: HS xác định được nhu cầu thông tin và thực hiện tìm kiếm đơn giản trong môi trường số dưới sự hướng dẫn; biết tìm bài thơ/câu chuyện thiếu nhi phù hợp, chọn nguồn đọc an toàn, rõ tên bài, tác giả hoặc địa chỉ nguồn.</t>
-        </is>
-      </c>
+      <c r="H26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1472,11 +1459,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.2 CB1a: HS biết chọn nguồn thông tin số đơn giản, tin cậy và tôn trọng bản quyền khi tìm bài viết/hình ảnh về hoạt động thể thao; không tự ý tải hình ảnh lạ, không sao chép tùy tiện và biết ghi nhớ tên bài, nguồn đọc.</t>
-        </is>
-      </c>
+      <c r="H34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -1719,11 +1702,7 @@
           <t>49</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 2.2 CB1a: HS nêu được điểm giống nhau giữa tấm thiệp, lời cảm ơn viết trên giấy và tin nhắn gửi bằng điện thoại.</t>
-        </is>
-      </c>
+      <c r="H42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -1992,12 +1971,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp AI 2.A1.2: HS nhận biết AI có thể gợi ý từ ngữ/dàn ý khi viết về con vật, nhưng chỉ dùng để tham khảo; HS phải tự quan sát, tự viết bằng lời của mình, không nhập thông tin riêng tư của gia đình.
-Năng lực số 5.2 CB1b: HS nói ý theo từng ô của sơ đồ để GV gõ vào, rồi dựa vào dàn ý trên màn hình mà viết đoạn văn của mình.</t>
-        </is>
-      </c>
+      <c r="H51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -2207,11 +2181,7 @@
           <t>69</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 3.1 CB1a: HS đọc bài viết được chiếu trên màn hình, nói được một câu kể rõ việc của bạn và một chỗ cần bổ sung.</t>
-        </is>
-      </c>
+      <c r="H58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -2454,11 +2424,7 @@
           <t>79</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát ảnh phóng to và nêu được chi tiết mình sẽ đưa vào bài tả.</t>
-        </is>
-      </c>
+      <c r="H66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -2882,12 +2848,7 @@
           <t>100</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp AI (2.A1.2): HS nhận biết AI có thể hỗ trợ gợi ý ý tưởng theo khung câu hỏi khi viết đoạn giới thiệu đồ dùng học tập; biết sử dụng gợi ý ở mức tham khảo, không chép máy móc.
-Năng lực số 5.2 CB1b: HS nói ý theo từng ô của sơ đồ để GV gõ vào, rồi dựa vào dàn ý trên màn hình mà viết đoạn văn của mình.</t>
-        </is>
-      </c>
+      <c r="H80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -4895,11 +4856,7 @@
           <t>190</t>
         </is>
       </c>
-      <c r="H145" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1a: HS chọn bài đọc về thiếu nhi trong kho sách điện tử GV mở sẵn và nói vì sao chọn bài đó.</t>
-        </is>
-      </c>
+      <c r="H145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -5146,11 +5103,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="H153" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp AI - YCCĐ 2.A2.1: HS biết mục đích của AI trong gia đình là hỗ trợ con người, giúp tiết kiệm thời gian, giảm một số công việc nhà; con người vẫn cần sử dụng đúng mục đích và kiểm tra kết quả.</t>
-        </is>
-      </c>
+      <c r="H153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -5873,11 +5826,7 @@
           <t>229-230</t>
         </is>
       </c>
-      <c r="H176" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 2.2 CB1a: HS nêu được điểm giống nhau giữa tấm thiệp, lời cảm ơn viết trên giấy và tin nhắn gửi bằng điện thoại.</t>
-        </is>
-      </c>
+      <c r="H176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -6316,11 +6265,7 @@
           <t>249-250</t>
         </is>
       </c>
-      <c r="H190" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 3.1 CB1a: HS đọc bài viết được chiếu trên màn hình, nói được một câu kể rõ việc của bạn và một chỗ cần bổ sung.</t>
-        </is>
-      </c>
+      <c r="H190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -6539,11 +6484,7 @@
           <t>259-260</t>
         </is>
       </c>
-      <c r="H197" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát ảnh phóng to và nêu được chi tiết mình sẽ đưa vào bài tả.</t>
-        </is>
-      </c>
+      <c r="H197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -7070,12 +7011,7 @@
           <t>289</t>
         </is>
       </c>
-      <c r="H214" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp năng lực số/an toàn thiết bị: Biết đọc một số thông tin đơn giản trên bản hướng dẫn sử dụng; nhận biết cần hỏi người lớn trước khi dùng thiết bị điện, thiết bị số.
-Tích hợp AI - YCCĐ 2.A3.2: Biết công cụ AI có thể gợi ý thông tin nhưng cần người lớn hướng dẫn, kiểm tra; không tự làm theo hướng dẫn nguy hiểm hoặc chia sẻ thông tin riêng tư.</t>
-        </is>
-      </c>
+      <c r="H214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -7315,11 +7251,7 @@
           <t>299</t>
         </is>
       </c>
-      <c r="H222" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 2.2 CB1a: HS nêu được vì sao phải kiểm tra tên người nhận trước khi gửi và vì sao mình cần nhờ bố mẹ gửi giúp.</t>
-        </is>
-      </c>
+      <c r="H222" s="4" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
@@ -7805,11 +7737,7 @@
           <t>319</t>
         </is>
       </c>
-      <c r="H238" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát ảnh phóng to và nêu được chi tiết mình sẽ đưa vào bài tả.</t>
-        </is>
-      </c>
+      <c r="H238" s="4" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
@@ -8049,11 +7977,7 @@
           <t>329</t>
         </is>
       </c>
-      <c r="H246" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB1b: HS nói ý theo từng ô của sơ đồ để GV gõ vào, rồi dựa vào dàn ý trên màn hình mà viết đoạn văn của mình.</t>
-        </is>
-      </c>
+      <c r="H246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">

--- a/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
+++ b/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
@@ -4670,11 +4670,7 @@
           <t>183</t>
         </is>
       </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 3.1 CB1a: HS quan sát GV thao tác quay và phát lại.</t>
-        </is>
-      </c>
+      <c r="H139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -4702,7 +4698,7 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS xem lại đoạn phim của mình và nói được một điều mình sẽ sửa khi nói trước lớp lần sau.</t>
+          <t>Năng lực số 3.1 CB1a: HS quan sát GV thao tác quay và phát lại.</t>
         </is>
       </c>
     </row>
@@ -4795,11 +4791,7 @@
           <t>188</t>
         </is>
       </c>
-      <c r="H143" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB1b: HS chọn từ chỉ sự vật trên màn hình, xem máy báo đúng – sai rồi tự sửa lựa chọn của mình.</t>
-        </is>
-      </c>
+      <c r="H143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -4917,11 +4909,7 @@
           <t>193</t>
         </is>
       </c>
-      <c r="H147" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS kể chuyện theo bộ tranh chiếu trên màn hình, kể đúng thứ tự các sự việc.</t>
-        </is>
-      </c>
+      <c r="H147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -4949,7 +4937,7 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS kể lời của mình theo tranh chạy trên màn hình rồi nghe bản kể mẫu và nói được mình học thêm được điều gì.</t>
+          <t>Năng lực số 1.1 CB1b: HS kể chuyện theo bộ tranh chiếu trên màn hình, kể đúng thứ tự các sự việc.</t>
         </is>
       </c>
     </row>
@@ -5042,11 +5030,7 @@
           <t>198</t>
         </is>
       </c>
-      <c r="H151" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB1b: HS chọn từ chỉ hoạt động trên màn hình, xem máy báo đúng – sai rồi tự sửa lựa chọn của mình.</t>
-        </is>
-      </c>
+      <c r="H151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -5164,12 +5148,7 @@
           <t>203</t>
         </is>
       </c>
-      <c r="H155" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp AI 2.A1.2: HS nhận biết công cụ AI có thể hỗ trợ gợi ý trình tự kể chuyện theo tranh hoặc gợi ý từ ngữ kể chuyện, nhưng HS phải kiểm tra lại với tranh SGK, tự kể bằng lời của mình, không sao chép nguyên văn.
-Năng lực số 3.1 CB1a: HS quan sát GV thao tác quay và phát lại.</t>
-        </is>
-      </c>
+      <c r="H155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -5197,7 +5176,8 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS kể lại câu chuyện theo tranh chiếu trên màn hình, kể đúng thứ tự các sự việc.</t>
+          <t>Tích hợp AI 2.A1.2: HS nhận biết công cụ AI có thể hỗ trợ gợi ý trình tự kể chuyện theo tranh hoặc gợi ý từ ngữ kể chuyện, nhưng HS phải kiểm tra lại với tranh SGK, tự kể bằng lời của mình, không sao chép nguyên văn.
+Năng lực số 3.1 CB1a: HS quan sát GV thao tác quay và phát lại.</t>
         </is>
       </c>
     </row>
@@ -5261,11 +5241,7 @@
           <t>207</t>
         </is>
       </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB1b: HS kéo - thả từ vào đúng ô theo hướng dẫn của GV và nghĩ thêm được từ cho ô còn thiếu.</t>
-        </is>
-      </c>
+      <c r="H158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -5293,7 +5269,7 @@
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS nhìn cặp ảnh trên màn hình và tìm được từ chỉ đặc điểm nói đúng điều mình quan sát.</t>
+          <t>Năng lực số 5.2 CB1b: HS kéo - thả từ vào đúng ô theo hướng dẫn của GV và nghĩ thêm được từ cho ô còn thiếu.</t>
         </is>
       </c>
     </row>
@@ -5351,11 +5327,7 @@
           <t>210</t>
         </is>
       </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1a: HS xác định được nhu cầu thông tin và thực hiện tìm kiếm đơn giản trong môi trường số dưới sự hướng dẫn; biết tìm bài thơ/câu chuyện thiếu nhi phù hợp, chọn nguồn đọc an toàn, rõ tên bài, tác giả hoặc địa chỉ nguồn.</t>
-        </is>
-      </c>
+      <c r="H161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -5416,12 +5388,7 @@
           <t>213</t>
         </is>
       </c>
-      <c r="H163" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp AI 2.A1.2: HS nhận biết công cụ AI có thể hỗ trợ gợi ý trình tự kể chuyện theo tranh hoặc gợi ý từ ngữ kể chuyện, nhưng HS phải kiểm tra lại với tranh SGK, tự kể bằng lời của mình, không sao chép nguyên văn và không nhập thông tin riêng tư.
-Năng lực số 3.1 CB1a: HS quan sát GV thao tác quay và phát lại.</t>
-        </is>
-      </c>
+      <c r="H163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -5449,7 +5416,8 @@
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS kể lời của mình theo tranh chạy trên màn hình rồi nghe bản kể mẫu và nói được mình học thêm được điều gì.</t>
+          <t>Tích hợp AI 2.A1.2: HS nhận biết công cụ AI có thể hỗ trợ gợi ý trình tự kể chuyện theo tranh hoặc gợi ý từ ngữ kể chuyện, nhưng HS phải kiểm tra lại với tranh SGK, tự kể bằng lời của mình, không sao chép nguyên văn và không nhập thông tin riêng tư.
+Năng lực số 3.1 CB1a: HS quan sát GV thao tác quay và phát lại.</t>
         </is>
       </c>
     </row>
@@ -5513,11 +5481,7 @@
           <t>217</t>
         </is>
       </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB1b: HS kéo - thả từ vào đúng ô theo hướng dẫn của GV và nghĩ thêm được từ cho ô còn thiếu.</t>
-        </is>
-      </c>
+      <c r="H166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -5545,8 +5509,7 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI - YCCĐ 2.D1.1: HS nêu được tình huống đơn giản trong đời sống có thể áp dụng AI để hỗ trợ luyện tập thể thao, đếm lượt tập hoặc gợi ý bài rèn luyện; biết AI chỉ hỗ trợ, con người vẫn cần cố gắng, chơi trung thực và kiểm tra kết quả.
-Năng lực số 1.1 CB1b: HS xem phim câm rồi nghe lại có tiếng, nêu thêm được từ ngữ mới đúng chủ điểm.</t>
+          <t>Năng lực số 5.2 CB1b: HS kéo - thả từ vào đúng ô theo hướng dẫn của GV và nghĩ thêm được từ cho ô còn thiếu.</t>
         </is>
       </c>
     </row>
@@ -5574,11 +5537,7 @@
           <t>219</t>
         </is>
       </c>
-      <c r="H168" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1a: HS biết tìm kiếm nội dung đơn giản trong môi trường số; biết tìm đọc bài thơ về vẻ đẹp thiên nhiên trên nguồn học liệu số do GV/cha mẹ cung cấp, chọn nội dung phù hợp và không bấm vào liên kết lạ.</t>
-        </is>
-      </c>
+      <c r="H168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -5606,7 +5565,7 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB1a: HS biết chọn nguồn thông tin số đơn giản, tin cậy và tôn trọng bản quyền khi tìm bài viết/hình ảnh về hoạt động thể thao; không tự ý tải hình ảnh lạ, không sao chép tùy tiện và biết ghi nhớ tên bài, nguồn đọc.</t>
+          <t>Năng lực số 1.1 CB1a: HS biết tìm kiếm nội dung đơn giản trong môi trường số; biết tìm đọc bài thơ về vẻ đẹp thiên nhiên trên nguồn học liệu số do GV/cha mẹ cung cấp, chọn nội dung phù hợp và không bấm vào liên kết lạ.</t>
         </is>
       </c>
     </row>
@@ -5669,12 +5628,7 @@
           <t>223</t>
         </is>
       </c>
-      <c r="H171" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp AI 2.A1.2: HS nhận biết công cụ AI như ChatGPT/Gemini có thể gợi ý trình tự kể chuyện theo tranh hoặc từ ngữ kể chuyện, nhưng HS phải kiểm tra với tranh SGK, tự kể bằng lời của mình, không sao chép nguyên văn và không nhập thông tin riêng tư.
-Năng lực số 1.1 CB1b: HS kể chuyện theo bộ tranh chiếu trên màn hình, kể đúng thứ tự các sự việc.</t>
-        </is>
-      </c>
+      <c r="H171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -5702,7 +5656,8 @@
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS kể lời của mình theo tranh chạy trên màn hình rồi nghe bản kể mẫu và nói được mình học thêm được điều gì.</t>
+          <t>Tích hợp AI 2.A1.2: HS nhận biết công cụ AI như ChatGPT/Gemini có thể gợi ý trình tự kể chuyện theo tranh hoặc từ ngữ kể chuyện, nhưng HS phải kiểm tra với tranh SGK, tự kể bằng lời của mình, không sao chép nguyên văn và không nhập thông tin riêng tư.
+Năng lực số 1.1 CB1b: HS kể chuyện theo bộ tranh chiếu trên màn hình, kể đúng thứ tự các sự việc.</t>
         </is>
       </c>
     </row>
@@ -5765,12 +5720,7 @@
           <t>227</t>
         </is>
       </c>
-      <c r="H174" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp AI 2.C3.1: HS nhận biết AI có thể hỗ trợ nhận diện hoặc phân loại con vật qua hình ảnh nhưng có thể nhầm; HS cần quan sát đặc điểm và kiểm tra lại với nguồn tin đáng tin cậy.
-Năng lực số 1.1 CB1a: HS biết tìm kiếm nội dung đơn giản về động vật hoang dã trên nguồn học liệu an toàn; biết ghi tên loài vật, thức ăn, nơi sống theo sơ đồ gợi ý.</t>
-        </is>
-      </c>
+      <c r="H174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -5796,11 +5746,7 @@
           <t>228</t>
         </is>
       </c>
-      <c r="H175" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 2.3 CB1a: HS biết công cụ số có thể nhắc lịch, xem thời khóa biểu nhưng chỉ sử dụng dưới sự hướng dẫn của người lớn và không chia sẻ thông tin cá nhân.</t>
-        </is>
-      </c>
+      <c r="H175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -5826,7 +5772,12 @@
           <t>229-230</t>
         </is>
       </c>
-      <c r="H176" s="4" t="inlineStr"/>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp AI 2.C3.1: HS nhận biết AI có thể hỗ trợ nhận diện hoặc phân loại con vật qua hình ảnh nhưng có thể nhầm; HS cần quan sát đặc điểm và kiểm tra lại với nguồn tin đáng tin cậy.
+Năng lực số 1.1 CB1a: HS biết tìm kiếm nội dung đơn giản về động vật hoang dã trên nguồn học liệu an toàn; biết ghi tên loài vật, thức ăn, nơi sống theo sơ đồ gợi ý.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -5887,12 +5838,7 @@
           <t>233</t>
         </is>
       </c>
-      <c r="H178" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp AI 2.A1.2: HS nhận biết công cụ AI như ChatGPT/Gemini có thể hỗ trợ gợi ý trình tự kể chuyện theo tranh, nhưng HS phải đối chiếu với tranh SGK, tự kể bằng lời của mình, không sao chép nguyên văn và không nhập thông tin riêng tư.
-Năng lực số 1.1 CB1b: HS kể chuyện theo bộ tranh chiếu trên màn hình, kể đúng thứ tự các sự việc.</t>
-        </is>
-      </c>
+      <c r="H178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -5920,7 +5866,8 @@
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS kể được điều mình đã trải qua khi ảnh của mình hiện lên màn hình.</t>
+          <t>Tích hợp AI 2.A1.2: HS nhận biết công cụ AI như ChatGPT/Gemini có thể hỗ trợ gợi ý trình tự kể chuyện theo tranh, nhưng HS phải đối chiếu với tranh SGK, tự kể bằng lời của mình, không sao chép nguyên văn và không nhập thông tin riêng tư.
+Năng lực số 1.1 CB1b: HS kể chuyện theo bộ tranh chiếu trên màn hình, kể đúng thứ tự các sự việc.</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5930,7 @@
           <t>237</t>
         </is>
       </c>
-      <c r="H181" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp AI 2.A1.2: HS nhận biết AI có thể gợi ý từ ngữ/dàn ý khi viết về con vật, nhưng chỉ dùng để tham khảo; HS phải tự quan sát, tự viết bằng lời của mình, không nhập thông tin riêng tư của gia đình.
-Năng lực số 5.2 CB1b: HS nói ý theo từng ô của sơ đồ để GV gõ vào, rồi dựa vào dàn ý trên màn hình mà viết đoạn văn của mình.</t>
-        </is>
-      </c>
+      <c r="H181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -6016,7 +5958,8 @@
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1b: HS chọn đúng từ để hoàn thành câu nêu đặc điểm và đọc lại câu hoàn chỉnh.</t>
+          <t>Tích hợp AI 2.A1.2: HS nhận biết AI có thể gợi ý từ ngữ/dàn ý khi viết về con vật, nhưng chỉ dùng để tham khảo; HS phải tự quan sát, tự viết bằng lời của mình, không nhập thông tin riêng tư của gia đình.
+Năng lực số 5.2 CB1b: HS nói ý theo từng ô của sơ đồ để GV gõ vào, rồi dựa vào dàn ý trên màn hình mà viết đoạn văn của mình.</t>
         </is>
       </c>
     </row>
@@ -6044,11 +5987,7 @@
           <t>239-240</t>
         </is>
       </c>
-      <c r="H183" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 4.2 CB1a: HS biết họ tên, lớp, tổ, thông tin tham gia hoạt động là thông tin cần dùng đúng mục đích; không tự ý đăng, gửi danh sách của bạn lên mạng.</t>
-        </is>
-      </c>
+      <c r="H183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -6109,11 +6048,7 @@
           <t>243</t>
         </is>
       </c>
-      <c r="H185" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 3.1 CB1a: HS quan sát GV thao tác quay và phát lại.</t>
-        </is>
-      </c>
+      <c r="H185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -6141,7 +6076,7 @@
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS kể lời của mình theo tranh chạy trên màn hình rồi nghe bản kể mẫu và nói được mình học thêm được điều gì.</t>
+          <t>Năng lực số 3.1 CB1a: HS quan sát GV thao tác quay và phát lại.</t>
         </is>
       </c>
     </row>
@@ -6205,11 +6140,7 @@
           <t>247</t>
         </is>
       </c>
-      <c r="H188" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 2.2 CB1a: HS nêu được điểm giống nhau giữa tấm thiệp, lời cảm ơn viết trên giấy và tin nhắn gửi bằng điện thoại.</t>
-        </is>
-      </c>
+      <c r="H188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -6235,11 +6166,7 @@
           <t>248</t>
         </is>
       </c>
-      <c r="H189" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB1b: HS nêu đáp án để GV thao tác trên máy, xem máy báo đúng - sai và tự sửa lại lựa chọn của mình.</t>
-        </is>
-      </c>
+      <c r="H189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -6265,7 +6192,11 @@
           <t>249-250</t>
         </is>
       </c>
-      <c r="H190" s="4" t="inlineStr"/>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 2.2 CB1a: HS nêu được điểm giống nhau giữa tấm thiệp, lời cảm ơn viết trên giấy và tin nhắn gửi bằng điện thoại.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -6327,11 +6258,7 @@
           <t>253</t>
         </is>
       </c>
-      <c r="H192" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 3.1 CB1a: HS quan sát GV thao tác quay và phát lại.</t>
-        </is>
-      </c>
+      <c r="H192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -6359,7 +6286,7 @@
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS kể lại câu chuyện theo tranh chiếu trên màn hình, kể đúng thứ tự các sự việc.</t>
+          <t>Năng lực số 3.1 CB1a: HS quan sát GV thao tác quay và phát lại.</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6350,7 @@
           <t>257</t>
         </is>
       </c>
-      <c r="H195" s="4" t="inlineStr">
-        <is>
-          <t>Tích hợp AI 2.A1.2: HS nhận biết AI có thể gợi ý dàn ý/từ ngữ khi viết đoạn văn bảo vệ môi trường, nhưng chỉ dùng tham khảo; HS phải tự viết bằng trải nghiệm thật và không nhập thông tin riêng tư.
-Năng lực số 3.1 CB1a: HS đọc bài viết được chiếu trên màn hình, nói được một câu kể rõ việc của bạn và một chỗ cần bổ sung.</t>
-        </is>
-      </c>
+      <c r="H195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -6454,11 +6376,7 @@
           <t>258</t>
         </is>
       </c>
-      <c r="H196" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS nhìn cặp ảnh trên màn hình và tìm được từ chỉ đặc điểm nói đúng điều mình quan sát.</t>
-        </is>
-      </c>
+      <c r="H196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -6484,7 +6402,12 @@
           <t>259-260</t>
         </is>
       </c>
-      <c r="H197" s="4" t="inlineStr"/>
+      <c r="H197" s="4" t="inlineStr">
+        <is>
+          <t>Tích hợp AI 2.A1.2: HS nhận biết AI có thể gợi ý dàn ý/từ ngữ khi viết đoạn văn bảo vệ môi trường, nhưng chỉ dùng tham khảo; HS phải tự viết bằng trải nghiệm thật và không nhập thông tin riêng tư.
+Năng lực số 3.1 CB1a: HS đọc bài viết được chiếu trên màn hình, nói được một câu kể rõ việc của bạn và một chỗ cần bổ sung.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -6699,11 +6622,7 @@
           <t>273</t>
         </is>
       </c>
-      <c r="H204" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS kể chuyện theo bộ tranh chiếu trên màn hình, kể đúng thứ tự các sự việc.</t>
-        </is>
-      </c>
+      <c r="H204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -6731,7 +6650,7 @@
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS kể lời của mình theo tranh chạy trên màn hình rồi nghe bản kể mẫu và nói được mình học thêm được điều gì.</t>
+          <t>Năng lực số 1.1 CB1b: HS kể chuyện theo bộ tranh chiếu trên màn hình, kể đúng thứ tự các sự việc.</t>
         </is>
       </c>
     </row>
@@ -22941,7 +22860,7 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI - YCCĐ 2.C1.2: Hiểu AI cần “học” từ các ví dụ (dữ liệu) để thực hiện nhiệm vụ.
+          <t>Tích hợp AI - YCCĐ 2.A2.1: Nhận biết các thiết bị AI hỗ trợ giải phóng sức lao động trong gia đình.
 Năng lực số 3.1 CB1a: HS xem triển lãm ảnh sản phẩm của lớp, bình chọn và nói được vì sao mình chọn sản phẩm đó.</t>
         </is>
       </c>
@@ -24002,11 +23921,7 @@
           <t>43</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 3.1 CB1b: HS chọn cách giới thiệu sản phẩm/hình ảnh theo chủ điểm bằng phương tiện số đơn giản.</t>
-        </is>
-      </c>
+      <c r="H46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -24038,8 +23953,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Tích hợp AI - YCCĐ 2.C3.1: HS biết AI hỗ trợ phân loại, gợi ý trang phục dựa trên dữ liệu; con người phải kiểm tra và quyết định.
-Năng lực số 1.1 CB1b: HS đọc bản tin thời tiết chiếu trên màn hình và chọn được trang phục, đồ dùng hợp với thời tiết những ngày tới.</t>
+          <t>Năng lực số 5.2 CB1a: Nhận biết công cụ số đơn giản như đồng hồ báo thức, lịch hoặc ứng dụng nhắc việc có thể hỗ trợ tự giác học tập, sinh hoạt dưới sự hướng dẫn của người lớn.</t>
         </is>
       </c>
     </row>
@@ -24143,7 +24057,8 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1a: Nhận biết công cụ số đơn giản như đồng hồ báo thức, lịch hoặc ứng dụng nhắc việc có thể hỗ trợ tự giác học tập, sinh hoạt dưới sự hướng dẫn của người lớn.</t>
+          <t>Tích hợp AI - YCCĐ 2.C3.1: HS biết AI hỗ trợ phân loại, gợi ý trang phục dựa trên dữ liệu; con người phải kiểm tra và quyết định.
+Năng lực số 1.1 CB1b: HS đọc bản tin thời tiết chiếu trên màn hình và chọn được trang phục, đồ dùng hợp với thời tiết những ngày tới.</t>
         </is>
       </c>
     </row>
@@ -24177,7 +24092,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1b: HS chọn cách giới thiệu sản phẩm/hình ảnh theo chủ điểm bằng phương tiện số đơn giản.
+          <t>Năng lực số 3.1 CB1a: HS xem bộ ảnh trình diễn và nói được trang phục nào hợp với hoàn cảnh nào.
 KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
         </is>
       </c>
@@ -24865,7 +24780,9 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 4.2 CB1a: Nhận biết cách sử dụng và chia sẻ thông tin định danh cá nhân an toàn; không chia sẻ địa chỉ nhà, số điện thoại hoặc thông tin cá nhân cho người lạ trên môi trường số.
+          <t>Năng lực số 5.2 CB1a: Sử dụng công cụ số đơn giản để giải quyết nhu cầu cá nhân dưới sự hướng dẫn; biết điện thoại thông minh, bản đồ hoặc định vị có thể hỗ trợ tìm đường, gửi vị trí cho người thân khi gặp sự cố.
+Năng lực số 4.2 CB1a: Nhận biết cách bảo vệ thông tin định danh cá nhân; biết địa chỉ nhà, số điện thoại của bố mẹ và thông tin liên lạc khẩn cấp chỉ dùng để nhờ người tin cậy hỗ trợ, không đăng công khai lên mạng.
+Tích hợp AI - YCCĐ 2.A1.1: Biết sử dụng công cụ tìm kiếm hoặc bản đồ AI để tìm trợ giúp khi cần.
 QTE: QTE: trẻ em có quyền được bảo vệ khỏi mọi hình thức xâm hại; nhớ số của người thân và Tổng đài quốc gia bảo vệ trẻ em 111.</t>
         </is>
       </c>
@@ -24969,9 +24886,7 @@
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1a: Sử dụng công cụ số đơn giản để giải quyết nhu cầu cá nhân dưới sự hướng dẫn; biết điện thoại thông minh, bản đồ hoặc định vị có thể hỗ trợ tìm đường, gửi vị trí cho người thân khi gặp sự cố.
-Năng lực số 4.2 CB1a: Nhận biết cách bảo vệ thông tin định danh cá nhân; biết địa chỉ nhà, số điện thoại của bố mẹ và thông tin liên lạc khẩn cấp chỉ dùng để nhờ người tin cậy hỗ trợ, không đăng công khai lên mạng.
-Tích hợp AI - YCCĐ 2.A1.1: Biết sử dụng công cụ tìm kiếm hoặc bản đồ AI để tìm trợ giúp khi cần.
+          <t>Năng lực số 4.2 CB1a: Nhận biết cách sử dụng và chia sẻ thông tin định danh cá nhân an toàn; không chia sẻ địa chỉ nhà, số điện thoại hoặc thông tin cá nhân cho người lạ trên môi trường số.
 ATGT: ATGT: đi thành hàng, bám sát người phụ trách khi ra khỏi trường; đội mũ bảo hiểm cài quai khi ngồi sau xe máy, xe đạp điện.</t>
         </is>
       </c>
@@ -25523,7 +25438,7 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1b: HS chọn cách giới thiệu sản phẩm/hình ảnh theo chủ điểm bằng phương tiện số đơn giản.
+          <t>Năng lực số 3.1 CB1a: HS chụp ảnh và báo số liệu cho GV ghi vào sổ chăm sóc cây của tổ mình.
 QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục biết ơn người có công với cách mạng; kính trọng cán bộ, chiến sĩ đang làm nhiệm vụ bảo vệ Tổ quốc.</t>
         </is>
       </c>
@@ -25558,8 +25473,7 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1b: HS chọn cách giới thiệu sản phẩm/hình ảnh theo chủ điểm bằng phương tiện số đơn giản.
-KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
+          <t>KNS: KN ứng phó với tình huống nguy hiểm và tìm kiếm sự trợ giúp.</t>
         </is>
       </c>
     </row>
@@ -25593,7 +25507,7 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 4.4 CB1a: Nhận biết tác động của công nghệ số đối với môi trường; biết thu gom pin cũ, thiết bị điện tử hỏng đúng nơi quy định.</t>
+          <t>Năng lực số 5.2 CB1a: Xác định nhu cầu cá nhân và sử dụng công cụ số đơn giản để trình bày kết quả; dưới sự hướng dẫn của GV, HS biết dùng bảng hoặc biểu tượng số đơn giản để trình bày kết quả khảo sát khu vực sạch - chưa sạch.</t>
         </is>
       </c>
     </row>
@@ -25627,7 +25541,8 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS chụp ảnh và báo số liệu cho GV ghi vào sổ chăm sóc cây của tổ mình.
+          <t>Tích hợp AI - YCCĐ 2.C3.1: HS biết AI có thể hỗ trợ phân loại rác thải tự động để bảo vệ môi trường.
+Năng lực số 3.1 CB1a: HS chụp ảnh và báo số liệu cho GV ghi vào sổ chăm sóc cây của tổ mình.
 KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
         </is>
       </c>
@@ -25697,117 +25612,117 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
+          <t>Năng lực số 4.4 CB1a: Nhận biết tác động của công nghệ số đối với môi trường; biết thu gom pin cũ, thiết bị điện tử hỏng đúng nơi quy định.
+KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr"/>
+      <c r="D96" s="4" t="inlineStr"/>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Sinh hoạt lớp: Nghề của mẹ, nghề của cha</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 3.1 CB1a: HS chụp ảnh và báo số liệu cho GV ghi vào sổ chăm sóc cây của tổ mình.
+KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Sinh hoạt dưới cờ: Hát, đọc thơ về nghề nghiệp</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB1b: HS tìm thông tin đơn giản về nghề nghiệp từ nguồn số phù hợp.
+KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr"/>
+      <c r="D98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Hoạt động giáo dục theo chủ đề: Nghề nào tính nấy</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
           <t>Tích hợp AI – YCCĐ 2.A1.2: Nhận biết trong nghề nghiệp thực tế, AI có thể hỗ trợ nhưng con người phải giám sát và chịu trách nhiệm.
 Năng lực số 1.1 CB1b: HS xem phim, gọi tên được một số nghề và nêu đức tính cần có của người làm nghề đó.
 KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="inlineStr"/>
-      <c r="D96" s="4" t="inlineStr"/>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>Sinh hoạt lớp: Nghề của mẹ, nghề của cha</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB1b: HS đoán đúng tên nghề qua câu đố và tiếng động trong trò chơi.
-KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr"/>
-      <c r="D97" s="4" t="inlineStr"/>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>Sinh hoạt dưới cờ: Hát, đọc thơ về nghề nghiệp</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS tìm thông tin đơn giản về nghề nghiệp từ nguồn số phù hợp.
-KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr"/>
-      <c r="D98" s="4" t="inlineStr"/>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>Hoạt động giáo dục theo chủ đề: Nghề nào tính nấy</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB1b: HS xem phim, gọi tên được một số nghề và nêu đức tính cần có của người làm nghề đó.
-KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
-        </is>
-      </c>
-    </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
@@ -25838,7 +25753,7 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS tìm thông tin đơn giản về nghề nghiệp từ nguồn số phù hợp.
+          <t>Năng lực số 5.2 CB1b: HS đoán đúng tên nghề qua câu đố và tiếng động trong trò chơi.
 KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
         </is>
       </c>
@@ -25908,7 +25823,7 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1a: Xác định nhu cầu cá nhân và sử dụng công cụ số đơn giản để trình bày kết quả; dưới sự hướng dẫn của GV, HS biết dùng bảng hoặc biểu tượng số đơn giản để trình bày kết quả khảo sát khu vực sạch - chưa sạch.
+          <t>Năng lực số 1.1 CB1b: HS xem phim, gọi tên được một số nghề và nêu đức tính cần có của người làm nghề đó.
 QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục biết ơn người có công với cách mạng; kính trọng cán bộ, chiến sĩ đang làm nhiệm vụ bảo vệ Tổ quốc.</t>
         </is>
       </c>
@@ -25943,7 +25858,7 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS tìm thông tin đơn giản về nghề nghiệp từ nguồn số phù hợp.
+          <t>Năng lực số 5.2 CB1b: HS đoán đúng tên nghề qua câu đố và tiếng động trong trò chơi.
 QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục biết ơn người có công với cách mạng; kính trọng cán bộ, chiến sĩ đang làm nhiệm vụ bảo vệ Tổ quốc.</t>
         </is>
       </c>

--- a/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
+++ b/assets/docs/lop2/KHDH ca khoi - Lop 2.xlsx
@@ -549,7 +549,7 @@
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Bài 1: TÔI LÀ HỌC SINH LỚP 2 – TIẾT 1 - 2: ĐỌC: TÔI LÀ HỌC SINH LỚP 2</t>
+          <t>Bài 1: Tôi là học sinh lớp 2 – Tiết 1 - 2: Đọc: Tôi là học sinh lớp 2</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -584,7 +584,7 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Bài 1: TÔI LÀ HỌC SINH LỚP 2 – TIẾT 3: VIẾT: CHỮ HOA A</t>
+          <t>Bài 1: Tôi là học sinh lớp 2 – Tiết 3: Viết: Chữ hoa A</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
@@ -610,7 +610,7 @@
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Bài 1: TÔI LÀ HỌC SINH LỚP 2 – TIẾT 4: NÓI VÀ NGHE: NHỮNG NGÀY HÈ CỦA EM</t>
+          <t>Bài 1: Tôi là học sinh lớp 2 – Tiết 4: Nói và nghe: Những ngày hè của em</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
@@ -640,7 +640,7 @@
       <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: NGÀY HÔM QUA ĐÂU RỒI? – TIẾT 1 - 2: ĐỌC: NGÀY HÔM QUA ĐÂU RỒI?</t>
+          <t>Bài 2: Ngày hôm qua đâu rồi? – Tiết 1 - 2: Đọc: Ngày hôm qua đâu rồi?</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -676,7 +676,7 @@
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: NGÀY HÔM QUA ĐÂU RỒI? – TIẾT 3: VIẾT: NGHE - VIẾT: NGÀY HÔM QUA ĐÂU RỒI?; BẢNG CHỮ CÁI</t>
+          <t>Bài 2: Ngày hôm qua đâu rồi? – Tiết 3: Viết: Nghe - Viết: Ngày hôm qua đâu rồi?; bảng chữ cái</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
@@ -702,7 +702,7 @@
       <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: NGÀY HÔM QUA ĐÂU RỒI? – TIẾT 4: TỪ NGỮ CHỈ SỰ VẬT, HOẠT ĐỘNG. CÂU GIỚI THIỆU</t>
+          <t>Bài 2: Ngày hôm qua đâu rồi? – Tiết 4: Từ ngữ chỉ sự vật, hoạt động. Câu giới thiệu</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
@@ -732,7 +732,7 @@
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: NGÀY HÔM QUA ĐÂU RỒI? – TIẾT 5: VIẾT ĐOẠN VĂN GIỚI THIỆU VỀ BẢN THÂN</t>
+          <t>Bài 2: Ngày hôm qua đâu rồi? – Tiết 5: Viết đoạn văn giới thiệu về bản thân</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
@@ -758,7 +758,7 @@
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: NGÀY HÔM QUA ĐÂU RỒI? – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 2: Ngày hôm qua đâu rồi? – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
@@ -788,7 +788,7 @@
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Bài 3: NIỀM VUI CỦA BI VÀ BỐNG – TIẾT 1 - 2: ĐỌC: NIỀM VUI CỦA BI VÀ BỐNG</t>
+          <t>Bài 3: Niềm vui của bi và bống – Tiết 1 - 2: Đọc: Niềm vui của bi và bống</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Bài 3: NIỀM VUI CỦA BI VÀ BỐNG – TIẾT 3: VIẾT: CHỮ HOA Ă, Â</t>
+          <t>Bài 3: Niềm vui của bi và bống – Tiết 3: Viết: Chữ hoa Ă, Â</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
@@ -849,7 +849,7 @@
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Bài 3: NIỀM VUI CỦA BI VÀ BỐNG – TIẾT 4: NÓI VÀ NGHE: KỂ CHUYỆN NIỀM VUI CỦA BI VÀ BỐNG</t>
+          <t>Bài 3: Niềm vui của bi và bống – Tiết 4: Nói và nghe: Kể chuyện niềm vui của bi và bống</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
@@ -879,7 +879,7 @@
       <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Bài 4: LÀM VIỆC THẬT LÀ VUI – TIẾT 1 - 2: ĐỌC: LÀM VIỆC THẬT LÀ VUI</t>
+          <t>Bài 4: Làm việc thật là vui – Tiết 1 - 2: Đọc: Làm việc thật là vui</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -914,7 +914,7 @@
       <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Bài 4: LÀM VIỆC THẬT LÀ VUI – TIẾT 3: VIẾT: NGHE - VIẾT: LÀM VIỆC THẬT LÀ VUI; BẢNG CHỮ CÁI</t>
+          <t>Bài 4: Làm việc thật là vui – Tiết 3: Viết: Nghe - Viết: Làm việc thật là vui; bảng chữ cái</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -940,7 +940,7 @@
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Bài 4: LÀM VIỆC THẬT LÀ VUI – TIẾT 4: LUYỆN TỪ VÀ CÂU: TỪ NGỮ CHỈ SỰ VẬT, HOẠT ĐỘNG; CÂU NÊU HOẠT ĐỘNG</t>
+          <t>Bài 4: Làm việc thật là vui – Tiết 4: Luyện từ và câu: Từ ngữ chỉ sự vật, hoạt động; câu nêu hoạt động</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -970,7 +970,7 @@
       <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Bài 4: LÀM VIỆC THẬT LÀ VUI – TIẾT 5: LUYỆN VIẾT ĐOẠN: KỂ MỘT VIỆC EM ĐÃ LÀM Ở NHÀ</t>
+          <t>Bài 4: Làm việc thật là vui – Tiết 5: Luyện viết đoạn: Kể một việc em đã làm ở nhà</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -1000,7 +1000,7 @@
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Bài 4: LÀM VIỆC THẬT LÀ VUI – TIẾT 6: ĐỌC MỞ RỘNG: BÀI VIẾT VỀ HOẠT ĐỘNG CỦA THIẾU NHI</t>
+          <t>Bài 4: Làm việc thật là vui – Tiết 6: Đọc mở rộng: Bài viết về hoạt động của thiếu nhi</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
@@ -1026,7 +1026,7 @@
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Bài 5: EM CÓ XINH KHÔNG? – TIẾT 1 - 2: ĐỌC: EM CÓ XINH KHÔNG?</t>
+          <t>Bài 5: Em có xinh không? – Tiết 1 - 2: Đọc: Em có xinh không?</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Bài 5: EM CÓ XINH KHÔNG? – TIẾT 3: VIẾT: CHỮ HOA B</t>
+          <t>Bài 5: Em có xinh không? – Tiết 3: Viết: Chữ hoa B</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bài 5: EM CÓ XINH KHÔNG? – TIẾT 4: NÓI VÀ NGHE: KỂ CHUYỆN EM CÓ XINH KHÔNG?</t>
+          <t>Bài 5: Em có xinh không? – Tiết 4: Nói và nghe: Kể chuyện em có xinh không?</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Bài 6: MỘT GIỜ HỌC – TIẾT 1 - 2: ĐỌC: MỘT GIỜ HỌC</t>
+          <t>Bài 6: Một giờ học – Tiết 1 - 2: Đọc: Một giờ học</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1154,7 +1154,7 @@
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Bài 6: MỘT GIỜ HỌC – TIẾT 3: VIẾT: NGHE - VIẾT MỘT GIỜ HỌC; BẢNG CHỮ CÁI</t>
+          <t>Bài 6: Một giờ học – Tiết 3: Viết: Nghe - Viết một giờ học; bảng chữ cái</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Bài 6: MỘT GIỜ HỌC – TIẾT 4: LUYỆN TỪ VÀ CÂU: TỪ CHỈ ĐẶC ĐIỂM; CÂU NÊU ĐẶC ĐIỂM</t>
+          <t>Bài 6: Một giờ học – Tiết 4: Luyện từ và câu: Từ chỉ đặc điểm; câu nêu đặc điểm</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Bài 6: MỘT GIỜ HỌC – TIẾT 5: LUYỆN VIẾT ĐOẠN: VIẾT ĐOẠN VĂN KỂ VIỆC THƯỜNG LÀM</t>
+          <t>Bài 6: Một giờ học – Tiết 5: Luyện viết đoạn: Viết đoạn văn kể việc thường làm</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -1236,7 +1236,7 @@
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Bài 6: MỘT GIỜ HỌC – TIẾT 6: ĐỌC MỞ RỘNG: BÀI THƠ, CÂU CHUYỆN VỀ TRẺ EM LÀM VIỆC NHÀ</t>
+          <t>Bài 6: Một giờ học – Tiết 6: Đọc mở rộng: Bài thơ, câu chuyện về trẻ em làm việc nhà</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Bài 7: CÂY XẤU HỔ – TIẾT 1 - 2: ĐỌC: CÂY XẤU HỔ</t>
+          <t>Bài 7: Cây xấu hổ – Tiết 1 - 2: Đọc: Cây xấu hổ</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1301,7 +1301,7 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bài 7: CÂY XẤU HỔ – TIẾT 3: VIẾT: CHỮ HOA C</t>
+          <t>Bài 7: Cây xấu hổ – Tiết 3: Viết: Chữ hoa C</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -1327,7 +1327,7 @@
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bài 7: CÂY XẤU HỔ – TIẾT 4: NÓI VÀ NGHE: KỂ CHUYỆN CHÚ ĐỖ CON</t>
+          <t>Bài 7: Cây xấu hổ – Tiết 4: Nói và nghe: Kể chuyện chú đỗ con</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bài 8: CẦU THỦ DỰ BỊ – TIẾT 1 - 2: ĐỌC: CẦU THỦ DỰ BỊ</t>
+          <t>Bài 8: Cầu thủ dự bị – Tiết 1 - 2: Đọc: Cầu thủ dự bị</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1393,7 +1393,7 @@
       <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bài 8: CẦU THỦ DỰ BỊ – TIẾT 3: VIẾT: NGHE - VIẾT CẦU THỦ DỰ BỊ; VIẾT HOA TÊN NGƯỜI</t>
+          <t>Bài 8: Cầu thủ dự bị – Tiết 3: Viết: Nghe - Viết cầu thủ dự bị; viết hoa tên người</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
@@ -1419,7 +1419,7 @@
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bài 8: CẦU THỦ DỰ BỊ – TIẾT 4: LUYỆN TỪ VÀ CÂU: MỞ RỘNG VỐN TỪ VỀ HOẠT ĐỘNG THỂ THAO, VUI CHƠI; CÂU NÊU HOẠT ĐỘNG</t>
+          <t>Bài 8: Cầu thủ dự bị – Tiết 4: Luyện từ và câu: Mở rộng vốn từ về hoạt động thể thao, vui chơi; câu nêu hoạt động</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr"/>
@@ -1450,7 +1450,7 @@
       <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bài 8: CẦU THỦ DỰ BỊ – TIẾT 5: LUYỆN VIẾT ĐOẠN: KỂ VỀ MỘT HOẠT ĐỘNG THỂ THAO HOẶC TRÒ CHƠI</t>
+          <t>Bài 8: Cầu thủ dự bị – Tiết 5: Luyện viết đoạn: Kể về một hoạt động thể thao hoặc trò chơi</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Bài 8: CẦU THỦ DỰ BỊ – TIẾT 6: ĐỌC MỞ RỘNG: BÀI VIẾT VỀ HOẠT ĐỘNG THỂ THAO</t>
+          <t>Bài 8: Cầu thủ dự bị – Tiết 6: Đọc mở rộng: Bài viết về hoạt động thể thao</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr"/>
@@ -1506,7 +1506,7 @@
       <c r="D36" s="4" t="inlineStr"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Bài 9: CÔ GIÁO LỚP EM – TIẾT 1 - 2: ĐỌC: CÔ GIÁO LỚP EM</t>
+          <t>Bài 9: Cô giáo lớp em – Tiết 1 - 2: Đọc: Cô giáo lớp em</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -1542,7 +1542,7 @@
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Bài 9: CÔ GIÁO LỚP EM – TIẾT 3: VIẾT: CHỮ HOA D</t>
+          <t>Bài 9: Cô giáo lớp em – Tiết 3: Viết: Chữ hoa D</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
@@ -1568,7 +1568,7 @@
       <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Bài 9: CÔ GIÁO LỚP EM – TIẾT 4: NÓI VÀ NGHE: KỂ CHUYỆN CẬU BÉ HAM HỌC</t>
+          <t>Bài 9: Cô giáo lớp em – Tiết 4: Nói và nghe: Kể chuyện cậu bé ham học</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       <c r="D39" s="4" t="inlineStr"/>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Bài 10: THỜI KHÓA BIỂU – TIẾT 1 - 2: ĐỌC: THỜI KHÓA BIỂU</t>
+          <t>Bài 10: Thời khóa biểu – Tiết 1 - 2: Đọc: Thời khóa biểu</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -1633,7 +1633,7 @@
       <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Bài 10: THỜI KHÓA BIỂU – TIẾT 3: VIẾT: NGHE - VIẾT: THỜI KHÓA BIỂU; PHÂN BIỆT C/K, CH/TR, V/D</t>
+          <t>Bài 10: Thời khóa biểu – Tiết 3: Viết: Nghe - Viết: Thời khóa biểu; phân biệt C/K, CH/TR, V/D</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bài 10: THỜI KHÓA BIỂU – TIẾT 4: LUYỆN TỪ VÀ CÂU: TỪ NGỮ CHỈ SỰ VẬT, HOẠT ĐỘNG; CÂU NÊU HOẠT ĐỘNG</t>
+          <t>Bài 10: Thời khóa biểu – Tiết 4: Luyện từ và câu: Từ ngữ chỉ sự vật, hoạt động; câu nêu hoạt động</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
@@ -1693,7 +1693,7 @@
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Bài 10: THỜI KHÓA BIỂU – TIẾT 5: LUYỆN VIẾT ĐOẠN: VIẾT THỜI GIAN BIỂU</t>
+          <t>Bài 10: Thời khóa biểu – Tiết 5: Luyện viết đoạn: Viết thời gian biểu</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
@@ -1719,7 +1719,7 @@
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Bài 10: THỜI KHÓA BIỂU – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 10: Thời khóa biểu – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -1749,7 +1749,7 @@
       <c r="D44" s="4" t="inlineStr"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Bài 11: CÁI TRỐNG TRƯỜNG EM – TIẾT 1 - 2: ĐỌC: CÁI TRỐNG TRƯỜNG EM</t>
+          <t>Bài 11: Cái trống trường em – Tiết 1 - 2: Đọc: Cái trống trường em</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Bài 11: CÁI TRỐNG TRƯỜNG EM – TIẾT 3: VIẾT: CHỮ HOA Đ</t>
+          <t>Bài 11: Cái trống trường em – Tiết 3: Viết: Chữ hoa Đ</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
@@ -1811,7 +1811,7 @@
       <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Bài 11: CÁI TRỐNG TRƯỜNG EM – TIẾT 4: NÓI VÀ NGHE: NGÔI TRƯỜNG CỦA EM</t>
+          <t>Bài 11: Cái trống trường em – Tiết 4: Nói và nghe: Ngôi trường của em</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
@@ -1841,7 +1841,7 @@
       <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Bài 12: DANH SÁCH HỌC SINH – TIẾT 1 - 2: ĐỌC: DANH SÁCH HỌC SINH</t>
+          <t>Bài 12: Danh sách học sinh – Tiết 1 - 2: Đọc: Danh sách học sinh</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Bài 12: DANH SÁCH HỌC SINH – TIẾT 3: VIẾT: NGHE - VIẾT: CÁI TRỐNG TRƯỜNG EM; PHÂN BIỆT G/GH, S/X, DẤU HỎI/DẤU NGÃ</t>
+          <t>Bài 12: Danh sách học sinh – Tiết 3: Viết: Nghe - Viết: Cái trống trường em; phân biệt G/GH, S/X, dấu hỏi/dấu ngã</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -1902,7 +1902,7 @@
       <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Bài 12: DANH SÁCH HỌC SINH – TIẾT 4: LUYỆN TỪ VÀ CÂU: TỪ NGỮ CHỈ SỰ VẬT, ĐẶC ĐIỂM; CÂU NÊU ĐẶC ĐIỂM</t>
+          <t>Bài 12: Danh sách học sinh – Tiết 4: Luyện từ và câu: Từ ngữ chỉ sự vật, đặc điểm; câu nêu đặc điểm</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
@@ -1932,7 +1932,7 @@
       <c r="D50" s="4" t="inlineStr"/>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Bài 12: DANH SÁCH HỌC SINH – TIẾT 5: LUYỆN VIẾT ĐOẠN: LẬP DANH SÁCH HỌC SINH (TỔ)</t>
+          <t>Bài 12: Danh sách học sinh – Tiết 5: Luyện viết đoạn: Lập danh sách học sinh (tổ)</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
@@ -1962,7 +1962,7 @@
       <c r="D51" s="4" t="inlineStr"/>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Bài 12: DANH SÁCH HỌC SINH – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 12: Danh sách học sinh – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr"/>
@@ -1988,7 +1988,7 @@
       <c r="D52" s="4" t="inlineStr"/>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Bài 13: YÊU LẮM TRƯỜNG ƠI! – TIẾT 1 - 2: ĐỌC: YÊU LẮM TRƯỜNG ƠI!</t>
+          <t>Bài 13: Yêu lắm trường ơi! – Tiết 1 - 2: Đọc: Yêu lắm trường ơi!</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2024,7 +2024,7 @@
       <c r="D53" s="4" t="inlineStr"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Bài 13: YÊU LẮM TRƯỜNG ƠI! – TIẾT 3: VIẾT: CHỮ HOA E, Ê</t>
+          <t>Bài 13: Yêu lắm trường ơi! – Tiết 3: Viết: Chữ hoa E, Ê</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
@@ -2050,7 +2050,7 @@
       <c r="D54" s="4" t="inlineStr"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Bài 13: YÊU LẮM TRƯỜNG ƠI! – TIẾT 4: NÓI VÀ NGHE: KỂ CHUYỆN BỮA ĂN TRƯA</t>
+          <t>Bài 13: Yêu lắm trường ơi! – Tiết 4: Nói và nghe: Kể chuyện bữa ăn trưa</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
@@ -2080,7 +2080,7 @@
       <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bài 14: EM HỌC VẼ – TIẾT 1 - 2: ĐỌC: EM HỌC VẼ</t>
+          <t>Bài 14: Em học vẽ – Tiết 1 - 2: Đọc: Em học vẽ</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2116,7 +2116,7 @@
       <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Bài 14: EM HỌC VẼ – TIẾT 3: VIẾT: NGHE - VIẾT: EM HỌC VẼ; PHÂN BIỆT NG/NGH, R/D/GI, AN/ANG</t>
+          <t>Bài 14: Em học vẽ – Tiết 3: Viết: Nghe - Viết: Em học vẽ; phân biệt NG/NGH, r/d/gi, an/ang</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
@@ -2142,7 +2142,7 @@
       <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Bài 14: EM HỌC VẼ – TIẾT 4: LUYỆN TỪ VÀ CÂU: TỪ NGỮ CHỈ SỰ VẬT; DẤU CHẤM, DẤU CHẤM HỎI</t>
+          <t>Bài 14: Em học vẽ – Tiết 4: Luyện từ và câu: Từ ngữ chỉ sự vật; dấu chấm, dấu chấm hỏi</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
@@ -2172,7 +2172,7 @@
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Bài 14: EM HỌC VẼ – TIẾT 5: LUYỆN VIẾT ĐOẠN</t>
+          <t>Bài 14: Em học vẽ – Tiết 5: Luyện viết đoạn</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr"/>
@@ -2198,7 +2198,7 @@
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Bài 14: EM HỌC VẼ – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 14: Em học vẽ – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
       <c r="D60" s="4" t="inlineStr"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Bài 15: CUỐN SÁCH CỦA EM – TIẾT 1 - 2: ĐỌC: CUỐN SÁCH CỦA EM</t>
+          <t>Bài 15: Cuốn sách của em – Tiết 1 - 2: Đọc: Cuốn sách của em</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -2263,7 +2263,7 @@
       <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Bài 15: CUỐN SÁCH CỦA EM – TIẾT 3: VIẾT: CHỮ HOA G</t>
+          <t>Bài 15: Cuốn sách của em – Tiết 3: Viết: Chữ hoa G</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       <c r="D62" s="4" t="inlineStr"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Bài 15: CUỐN SÁCH CỦA EM – TIẾT 4: NÓI VÀ NGHE: KỂ CHUYỆN HỌA MI, VẸT VÀ QUẠ</t>
+          <t>Bài 15: Cuốn sách của em – Tiết 4: Nói và nghe: Kể chuyện họa mi, vẹt và quạ</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -2323,7 +2323,7 @@
       <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Bài 16: KHI TRANG SÁCH MỞ RA – TIẾT 1 - 2: ĐỌC: KHI TRANG SÁCH MỞ RA</t>
+          <t>Bài 16: Khi trang sách mở ra – Tiết 1 - 2: Đọc: Khi trang sách mở ra</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2359,7 +2359,7 @@
       <c r="D64" s="4" t="inlineStr"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bài 16: KHI TRANG SÁCH MỞ RA – TIẾT 3: VIẾT: NGHE - VIẾT: KHI TRANG SÁCH MỞ RA; PHÂN BIỆT L/N, ĂN/ĂNG, ÂN/ÂNG</t>
+          <t>Bài 16: Khi trang sách mở ra – Tiết 3: Viết: Nghe - Viết: Khi trang sách mở ra; phân biệt L/N, ăn/ăng, ân/âng</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr"/>
@@ -2385,7 +2385,7 @@
       <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Bài 16: KHI TRANG SÁCH MỞ RA – TIẾT 4: LUYỆN TỪ VÀ CÂU: TỪ NGỮ CHỈ ĐẶC ĐIỂM; CÂU NÊU ĐẶC ĐIỂM; DẤU CHẤM, DẤU CHẤM HỎI</t>
+          <t>Bài 16: Khi trang sách mở ra – Tiết 4: Luyện từ và câu: Từ ngữ chỉ đặc điểm; câu nêu đặc điểm; dấu chấm, dấu chấm hỏi</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr"/>
@@ -2415,7 +2415,7 @@
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bài 16: KHI TRANG SÁCH MỞ RA – TIẾT 5: LUYỆN VIẾT ĐOẠN: TẢ ĐỒ DÙNG HỌC TẬP</t>
+          <t>Bài 16: Khi trang sách mở ra – Tiết 5: Luyện viết đoạn: Tả đồ dùng học tập</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
       <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bài 16: KHI TRANG SÁCH MỞ RA – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 16: Khi trang sách mở ra – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
       <c r="D68" s="4" t="inlineStr"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP GIỮA HỌC KÌ I – TIẾT 1 - 2</t>
+          <t>Ôn tập giữa học kì I – Tiết 1 - 2</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2505,7 +2505,7 @@
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP GIỮA HỌC KÌ I – TIẾT 3 - 4</t>
+          <t>Ôn tập giữa học kì I – Tiết 3 - 4</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       <c r="D70" s="4" t="inlineStr"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP GIỮA HỌC KÌ I – TIẾT 5 - 6</t>
+          <t>Ôn tập giữa học kì I – Tiết 5 - 6</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr"/>
@@ -2565,7 +2565,7 @@
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP GIỮA HỌC KÌ I – TIẾT 7 - 8</t>
+          <t>Ôn tập giữa học kì I – Tiết 7 - 8</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr"/>
@@ -2595,7 +2595,7 @@
       <c r="D72" s="4" t="inlineStr"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP GIỮA HỌC KÌ I – TIẾT 9 - 10</t>
+          <t>Ôn tập giữa học kì I – Tiết 9 - 10</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr"/>
@@ -2625,7 +2625,7 @@
       <c r="D73" s="4" t="inlineStr"/>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Bài 17: GỌI BẠN – TIẾT 1 - 2: ĐỌC: GỌI BẠN</t>
+          <t>Bài 17: Gọi bạn – Tiết 1 - 2: Đọc: Gọi bạn</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -2661,7 +2661,7 @@
       <c r="D74" s="4" t="inlineStr"/>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Bài 17: GỌI BẠN – TIẾT 3: VIẾT: CHỮ HOA H</t>
+          <t>Bài 17: Gọi bạn – Tiết 3: Viết: Chữ hoa H</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       <c r="D75" s="4" t="inlineStr"/>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Bài 17: GỌI BẠN – TIẾT 4: NÓI VÀ NGHE: KỂ CHUYỆN GỌI BẠN</t>
+          <t>Bài 17: Gọi bạn – Tiết 4: Nói và nghe: Kể chuyện gọi bạn</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
       <c r="D76" s="4" t="inlineStr"/>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Bài 18: TỚ NHỚ CẬU – TIẾT 1 - 2: ĐỌC: TỚ NHỚ CẬU</t>
+          <t>Bài 18: Tớ nhớ cậu – Tiết 1 - 2: Đọc: Tớ nhớ cậu</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -2753,7 +2753,7 @@
       <c r="D77" s="4" t="inlineStr"/>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Bài 18: TỚ NHỚ CẬU – TIẾT 3: VIẾT: NGHE - VIẾT: TỚ NHỚ CẬU; PHÂN BIỆT C/K, IÊU/ƯƠU, EN/ENG</t>
+          <t>Bài 18: Tớ nhớ cậu – Tiết 3: Viết: Nghe - Viết: Tớ nhớ cậu; phân biệt C/K, iêu/ươu, en/eng</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
       <c r="D78" s="4" t="inlineStr"/>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Bài 18: TỚ NHỚ CẬU – TIẾT 4: LUYỆN TỪ VÀ CÂU: MỞ RỘNG VỐN TỪ VỀ TÌNH CẢM BẠN BÈ; DẤU CHẤM, DẤU CHẤM HỎI, DẤU CHẤM THAN</t>
+          <t>Bài 18: Tớ nhớ cậu – Tiết 4: Luyện từ và câu: Mở rộng vốn từ về tình cảm bạn bè; dấu chấm, dấu chấm hỏi, dấu chấm than</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr"/>
@@ -2809,7 +2809,7 @@
       <c r="D79" s="4" t="inlineStr"/>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Bài 18: TỚ NHỚ CẬU – TIẾT 5: LUYỆN VIẾT ĐOẠN</t>
+          <t>Bài 18: Tớ nhớ cậu – Tiết 5: Luyện viết đoạn</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       <c r="D80" s="4" t="inlineStr"/>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Bài 18: TỚ NHỚ CẬU – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 18: Tớ nhớ cậu – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
       <c r="D81" s="4" t="inlineStr"/>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Bài 19: CHỮ A VÀ NHỮNG NGƯỜI BẠN – TIẾT 1 - 2: ĐỌC – CHỮ A VÀ NHỮNG NGƯỜI BẠN</t>
+          <t>Bài 19: Chữ A và những người bạn – Tiết 1 - 2: Đọc – Chữ A và những người bạn</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -2901,7 +2901,7 @@
       <c r="D82" s="4" t="inlineStr"/>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Bài 19: CHỮ A VÀ NHỮNG NGƯỜI BẠN – TIẾT 3: VIẾT – CHỮ HOA I, K</t>
+          <t>Bài 19: Chữ A và những người bạn – Tiết 3: Viết – Chữ hoa I, K</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr"/>
@@ -2927,7 +2927,7 @@
       <c r="D83" s="4" t="inlineStr"/>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Bài 19: CHỮ A VÀ NHỮNG NGƯỜI BẠN – TIẾT 4: NÓI VÀ NGHE – NIỀM VUI CỦA EM</t>
+          <t>Bài 19: Chữ A và những người bạn – Tiết 4: Nói và nghe – Niềm vui của em</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
       <c r="D84" s="4" t="inlineStr"/>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Bài 20: NHÍM NÂU KẾT BẠN – TIẾT 1 - 2: ĐỌC – NHÍM NÂU KẾT BẠN</t>
+          <t>Bài 20: Nhím nâu kết bạn – Tiết 1 - 2: Đọc – Nhím nâu kết bạn</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -2994,7 +2994,7 @@
       <c r="D85" s="4" t="inlineStr"/>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Bài 20: NHÍM NÂU KẾT BẠN – TIẾT 3: VIẾT – NGHE - VIẾT: NHÍM NÂU KẾT BẠN</t>
+          <t>Bài 20: Nhím nâu kết bạn – Tiết 3: Viết – Nghe - Viết: Nhím nâu kết bạn</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr"/>
@@ -3020,7 +3020,7 @@
       <c r="D86" s="4" t="inlineStr"/>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Bài 20: NHÍM NÂU KẾT BẠN – TIẾT 4: LUYỆN TỪ VÀ CÂU – TỪ CHỈ HOẠT ĐỘNG, TỪ CHỈ ĐẶC ĐIỂM</t>
+          <t>Bài 20: Nhím nâu kết bạn – Tiết 4: Luyện từ và câu – Từ chỉ hoạt động, từ chỉ đặc điểm</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       <c r="D87" s="4" t="inlineStr"/>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Bài 20: NHÍM NÂU KẾT BẠN – TIẾT 5 - 6: LUYỆN VIẾT ĐOẠN – ĐỌC MỞ RỘNG</t>
+          <t>Bài 20: Nhím nâu kết bạn – Tiết 5 - 6: Luyện viết đoạn – Đọc mở rộng</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr"/>
@@ -3081,7 +3081,7 @@
       <c r="D88" s="4" t="inlineStr"/>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Bài 21: THẢ DIỀU – Tiết 1 - 2: Đọc</t>
+          <t>Bài 21: Thả diều – Tiết 1 - 2: Đọc</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -3116,7 +3116,7 @@
       <c r="D89" s="4" t="inlineStr"/>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Bài 21: THẢ DIỀU – Tiết 3: Viết – Chữ hoa L</t>
+          <t>Bài 21: Thả diều – Tiết 3: Viết – Chữ hoa L</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr"/>
@@ -3142,7 +3142,7 @@
       <c r="D90" s="4" t="inlineStr"/>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Bài 21: THẢ DIỀU – Tiết 4: Nói và nghe – Kể chuyện Chúng mình là bạn</t>
+          <t>Bài 21: Thả diều – Tiết 4: Nói và nghe – Kể chuyện Chúng mình là bạn</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr"/>
@@ -3172,7 +3172,7 @@
       <c r="D91" s="4" t="inlineStr"/>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Bài 22: TỚ LÀ LÊ-GÔ – Tiết 1 - 2: Đọc</t>
+          <t>Bài 22: Tớ là Lê-gô – Tiết 1 - 2: Đọc</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3208,7 +3208,7 @@
       <c r="D92" s="4" t="inlineStr"/>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Bài 22: TỚ LÀ LÊ-GÔ – Tiết 3: Viết – Nghe viết: Đồ chơi yêu thích</t>
+          <t>Bài 22: Tớ là Lê-gô – Tiết 3: Viết – Nghe viết: Đồ chơi yêu thích</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr"/>
@@ -3238,7 +3238,7 @@
       <c r="D93" s="4" t="inlineStr"/>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Bài 22: TỚ LÀ LÊ-GÔ – Tiết 4: Luyện từ và câu – Từ ngữ chỉ sự vật; Câu nêu đặc điểm</t>
+          <t>Bài 22: Tớ là Lê-gô – Tiết 4: Luyện từ và câu – Từ ngữ chỉ sự vật; Câu nêu đặc điểm</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
       <c r="D94" s="4" t="inlineStr"/>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Bài 22: TỚ LÀ LÊ-GÔ – Tiết 5 - 6: Luyện viết đoạn; Đọc mở rộng</t>
+          <t>Bài 22: Tớ là Lê-gô – Tiết 5 - 6: Luyện viết đoạn; Đọc mở rộng</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr"/>
@@ -3298,7 +3298,7 @@
       <c r="D95" s="4" t="inlineStr"/>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Bài 23: RỒNG RẮN LÊN MÂY – Tiết 1 - 2: Đọc</t>
+          <t>Bài 23: Rồng rắn lên mây – Tiết 1 - 2: Đọc</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -3334,7 +3334,7 @@
       <c r="D96" s="4" t="inlineStr"/>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Bài 23: RỒNG RẮN LÊN MÂY – Tiết 3: Viết – Chữ hoa M</t>
+          <t>Bài 23: Rồng rắn lên mây – Tiết 3: Viết – Chữ hoa M</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       <c r="D97" s="4" t="inlineStr"/>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Bài 23: RỒNG RẮN LÊN MÂY – Tiết 4: Nói và nghe – Búp bê biết khóc</t>
+          <t>Bài 23: Rồng rắn lên mây – Tiết 4: Nói và nghe – Búp bê biết khóc</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr"/>
@@ -3390,7 +3390,7 @@
       <c r="D98" s="4" t="inlineStr"/>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Bài 24: NẶN ĐỒ CHƠI – Tiết 1 - 2: Đọc</t>
+          <t>Bài 24: Nặn đồ chơi – Tiết 1 - 2: Đọc</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -3425,7 +3425,7 @@
       <c r="D99" s="4" t="inlineStr"/>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Bài 24: NẶN ĐỒ CHƠI – Tiết 3: Viết – Nghe viết: Nặn đồ chơi; Phân biệt da/gia, l/x, uơn/uơng</t>
+          <t>Bài 24: Nặn đồ chơi – Tiết 3: Viết – Nghe viết: Nặn đồ chơi; Phân biệt da/gia, l/x, uơn/uơng</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr"/>
@@ -3451,7 +3451,7 @@
       <c r="D100" s="4" t="inlineStr"/>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Bài 24: NẶN ĐỒ CHƠI – Tiết 4: Luyện từ và câu – Từ ngữ về đồ chơi; Dấu phẩy</t>
+          <t>Bài 24: Nặn đồ chơi – Tiết 4: Luyện từ và câu – Từ ngữ về đồ chơi; Dấu phẩy</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
       <c r="D101" s="4" t="inlineStr"/>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Bài 24: NẶN ĐỒ CHƠI – Tiết 5 - 6: Luyện viết đoạn; Đọc mở rộng</t>
+          <t>Bài 24: Nặn đồ chơi – Tiết 5 - 6: Luyện viết đoạn; Đọc mở rộng</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr"/>
@@ -3512,7 +3512,7 @@
       <c r="D102" s="4" t="inlineStr"/>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Bài 25: SỰ TÍCH HOA TỈ MUỘI – Tiết 1 - 2: Đọc – SỰ TÍCH HOA TỈ MUỘI</t>
+          <t>Bài 25: Sự tích hoa tỉ muội – Tiết 1 - 2: Đọc – Sự tích hoa tỉ muội</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -3548,7 +3548,7 @@
       <c r="D103" s="4" t="inlineStr"/>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Bài 25: SỰ TÍCH HOA TỈ MUỘI – Tiết 3: Viết – CHỮ HOA N</t>
+          <t>Bài 25: Sự tích hoa tỉ muội – Tiết 3: Viết – Chữ hoa N</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr"/>
@@ -3574,7 +3574,7 @@
       <c r="D104" s="4" t="inlineStr"/>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Bài 25: SỰ TÍCH HOA TỈ MUỘI – Tiết 4: Nói và nghe – HAI ANH EM</t>
+          <t>Bài 25: Sự tích hoa tỉ muội – Tiết 4: Nói và nghe – Hai anh em</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr"/>
@@ -3604,7 +3604,7 @@
       <c r="D105" s="4" t="inlineStr"/>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Bài 26: EM MANG VỀ YÊU THƯƠNG – Tiết 1 - 2: Đọc – EM MANG VỀ YÊU THƯƠNG</t>
+          <t>Bài 26: Em mang về yêu thương – Tiết 1 - 2: Đọc – Em mang về yêu thương</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -3640,7 +3640,7 @@
       <c r="D106" s="4" t="inlineStr"/>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Bài 26: EM MANG VỀ YÊU THƯƠNG – Tiết 3: Viết – NGHE – VIẾT: EM MANG VỀ YÊU THƯƠNG</t>
+          <t>Bài 26: Em mang về yêu thương – Tiết 3: Viết – Nghe – Viết: Em mang về yêu thương</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr"/>
@@ -3666,7 +3666,7 @@
       <c r="D107" s="4" t="inlineStr"/>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Bài 26: EM MANG VỀ YÊU THƯƠNG – Tiết 4: Luyện tập – TỪ NGỮ VỀ NGƯỜI THÂN – TỪ CHỈ ĐẶC ĐIỂM</t>
+          <t>Bài 26: Em mang về yêu thương – Tiết 4: Luyện tập – Từ ngữ về người thân – Từ chỉ đặc điểm</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr"/>
@@ -3696,7 +3696,7 @@
       <c r="D108" s="4" t="inlineStr"/>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Bài 26: EM MANG VỀ YÊU THƯƠNG – Tiết 5 - 6: Viết đoạn – Đọc mở rộng – VIẾT VỀ NGƯỜI THÂN – ĐỌC BÀI THƠ VỀ TÌNH CẢM ANH CHỊ EM</t>
+          <t>Bài 26: Em mang về yêu thương – Tiết 5 - 6: Viết đoạn – Đọc mở rộng – Viết về người thân – Đọc bài thơ về tình cảm anh chị em</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr"/>
@@ -3727,7 +3727,7 @@
       <c r="D109" s="4" t="inlineStr"/>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Bài 27: MẸ – TIẾT 1 - 2: ĐỌC</t>
+          <t>Bài 27: Mẹ – Tiết 1 - 2: Đọc</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -3763,7 +3763,7 @@
       <c r="D110" s="4" t="inlineStr"/>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Bài 27: MẸ – TIẾT 3: VIẾT – CHỮ HOA O</t>
+          <t>Bài 27: Mẹ – Tiết 3: Viết – Chữ hoa O</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr"/>
@@ -3789,7 +3789,7 @@
       <c r="D111" s="4" t="inlineStr"/>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Bài 27: MẸ – TIẾT 4: NÓI VÀ NGHE – KỂ CHUYỆN SỰ TÍCH CÂY VÚ SỮA</t>
+          <t>Bài 27: Mẹ – Tiết 4: Nói và nghe – Kể chuyện sự tích cây vú sữa</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr"/>
@@ -3819,7 +3819,7 @@
       <c r="D112" s="4" t="inlineStr"/>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Bài 28: TRÒ CHƠI CỦA BỐ – TIẾT 1 - 2: ĐỌC</t>
+          <t>Bài 28: Trò chơi của bố – Tiết 1 - 2: Đọc</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -3855,7 +3855,7 @@
       <c r="D113" s="4" t="inlineStr"/>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Bài 28: TRÒ CHƠI CỦA BỐ – TIẾT 3: VIẾT – NGHE VIẾT: TRÒ CHƠI CỦA BỐ</t>
+          <t>Bài 28: Trò chơi của bố – Tiết 3: Viết – Nghe viết: Trò chơi của bố</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr"/>
@@ -3881,7 +3881,7 @@
       <c r="D114" s="4" t="inlineStr"/>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Bài 28: TRÒ CHƠI CỦA BỐ – TIẾT 4: LUYỆN TẬP – MỞ RỘNG VỐN TỪ VỀ TÌNH CẢM GIA ĐÌNH; DẤU CHẤM, DẤU CHẤM HỎI, DẤU CHẤM THAN</t>
+          <t>Bài 28: Trò chơi của bố – Tiết 4: Luyện tập – Mở rộng vốn từ về tình cảm gia đình; dấu chấm, dấu chấm hỏi, dấu chấm than</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr"/>
@@ -3911,7 +3911,7 @@
       <c r="D115" s="4" t="inlineStr"/>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Bài 28: TRÒ CHƠI CỦA BỐ – TIẾT 5: LUYỆN TẬP – VIẾT ĐOẠN VĂN THỂ HIỆN TÌNH CẢM VỚI NGƯỜI THÂN</t>
+          <t>Bài 28: Trò chơi của bố – Tiết 5: Luyện tập – Viết đoạn văn thể hiện tình cảm với người thân</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr"/>
@@ -3942,7 +3942,7 @@
       <c r="D116" s="4" t="inlineStr"/>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Bài 28: TRÒ CHƠI CỦA BỐ – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 28: Trò chơi của bố – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr"/>
@@ -3972,7 +3972,7 @@
       <c r="D117" s="4" t="inlineStr"/>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Bài 29: CÁNH CỬA NHỚ BÀ – TIẾT 1 - 2: ĐỌC</t>
+          <t>Bài 29: Cánh cửa nhớ bà – Tiết 1 - 2: Đọc</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -4007,7 +4007,7 @@
       <c r="D118" s="4" t="inlineStr"/>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Bài 29: CÁNH CỬA NHỚ BÀ – TIẾT 3: VIẾT – CHỮ HOA Ô, Ơ</t>
+          <t>Bài 29: Cánh cửa nhớ bà – Tiết 3: Viết – Chữ hoa Ô, Ơ</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr"/>
@@ -4037,7 +4037,7 @@
       <c r="D119" s="4" t="inlineStr"/>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Bài 29: CÁNH CỬA NHỚ BÀ – TIẾT 4: NÓI VÀ NGHE – KỂ CHUYỆN BÀ CHÁU</t>
+          <t>Bài 29: Cánh cửa nhớ bà – Tiết 4: Nói và nghe – Kể chuyện bà cháu</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr"/>
@@ -4067,7 +4067,7 @@
       <c r="D120" s="4" t="inlineStr"/>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Bài 30: THƯƠNG ÔNG – TIẾT 1 - 2: ĐỌC</t>
+          <t>Bài 30: Thương ông – Tiết 1 - 2: Đọc</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -4102,7 +4102,7 @@
       <c r="D121" s="4" t="inlineStr"/>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Bài 30: THƯƠNG ÔNG – TIẾT 3: VIẾT – NGHE VIẾT: THƯƠNG ÔNG</t>
+          <t>Bài 30: Thương ông – Tiết 3: Viết – Nghe viết: Thương ông</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr"/>
@@ -4132,7 +4132,7 @@
       <c r="D122" s="4" t="inlineStr"/>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Bài 30: THƯƠNG ÔNG – TIẾT 4: LUYỆN TẬP – TỪ NGỮ CHỈ SỰ VẬT, HOẠT ĐỘNG; CÂU NÊU HOẠT ĐỘNG</t>
+          <t>Bài 30: Thương ông – Tiết 4: Luyện tập – Từ ngữ chỉ sự vật, hoạt động; câu nêu hoạt động</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr"/>
@@ -4162,7 +4162,7 @@
       <c r="D123" s="4" t="inlineStr"/>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Bài 30: THƯƠNG ÔNG – TIẾT 5: LUYỆN TẬP – VIẾT ĐOẠN VĂN KỂ VIỆC LÀM CÙNG NGƯỜI THÂN</t>
+          <t>Bài 30: Thương ông – Tiết 5: Luyện tập – Viết đoạn văn kể việc làm cùng người thân</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr"/>
@@ -4193,7 +4193,7 @@
       <c r="D124" s="4" t="inlineStr"/>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Bài 30: THƯƠNG ÔNG – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 30: Thương ông – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr"/>
@@ -4223,7 +4223,7 @@
       <c r="D125" s="4" t="inlineStr"/>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Bài 31: ÁNH SÁNG CỦA YÊU THƯƠNG – TIẾT 1 – 2: ĐỌC</t>
+          <t>Bài 31: Ánh sáng của yêu thương – Tiết 1 – 2: Đọc</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -4259,7 +4259,7 @@
       <c r="D126" s="4" t="inlineStr"/>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Bài 31: ÁNH SÁNG CỦA YÊU THƯƠNG – TIẾT 3: VIẾT CHỮ HOA P</t>
+          <t>Bài 31: Ánh sáng của yêu thương – Tiết 3: Viết chữ hoa P</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr"/>
@@ -4285,7 +4285,7 @@
       <c r="D127" s="4" t="inlineStr"/>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Bài 31: ÁNH SÁNG CỦA YÊU THƯƠNG – TIẾT 4: NÓI VÀ NGHE</t>
+          <t>Bài 31: Ánh sáng của yêu thương – Tiết 4: Nói và nghe</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr"/>
@@ -4315,7 +4315,7 @@
       <c r="D128" s="4" t="inlineStr"/>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Bài 32: CHƠI CHONG CHÓNG – TIẾT 1 – 2: ĐỌC</t>
+          <t>Bài 32: Chơi chong chóng – Tiết 1 – 2: Đọc</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -4351,7 +4351,7 @@
       <c r="D129" s="4" t="inlineStr"/>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Bài 32: CHƠI CHONG CHÓNG – TIẾT 3: VIẾT</t>
+          <t>Bài 32: Chơi chong chóng – Tiết 3: Viết</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr"/>
@@ -4377,7 +4377,7 @@
       <c r="D130" s="4" t="inlineStr"/>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Bài 32: CHƠI CHONG CHÓNG – TIẾT 4: LUYỆN TẬP</t>
+          <t>Bài 32: Chơi chong chóng – Tiết 4: Luyện tập</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr"/>
@@ -4407,7 +4407,7 @@
       <c r="D131" s="4" t="inlineStr"/>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Bài 32: CHƠI CHONG CHÓNG – TIẾT 5: VIẾT TIN NHẮN</t>
+          <t>Bài 32: Chơi chong chóng – Tiết 5: Viết tin nhắn</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr"/>
@@ -4438,7 +4438,7 @@
       <c r="D132" s="4" t="inlineStr"/>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Bài 32: CHƠI CHONG CHÓNG – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 32: Chơi chong chóng – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr"/>
@@ -4468,7 +4468,7 @@
       <c r="D133" s="4" t="inlineStr"/>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP VÀ ĐÁNH GIÁ CUỐI HỌC KÌ 1 – PHẦN I – ÔN TẬP – TIẾT 1 – 2</t>
+          <t>Ôn tập và đánh giá cuối học kì 1 – Phần I – Ôn tập – Tiết 1 – 2</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -4502,7 +4502,7 @@
       <c r="D134" s="4" t="inlineStr"/>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP VÀ ĐÁNH GIÁ CUỐI HỌC KÌ 1 – PHẦN I – ÔN TẬP – TIẾT 3 – 4</t>
+          <t>Ôn tập và đánh giá cuối học kì 1 – Phần I – Ôn tập – Tiết 3 – 4</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr"/>
@@ -4532,7 +4532,7 @@
       <c r="D135" s="4" t="inlineStr"/>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP VÀ ĐÁNH GIÁ CUỐI HỌC KÌ 1 – PHẦN I – ÔN TẬP – TIẾT 5 – 6</t>
+          <t>Ôn tập và đánh giá cuối học kì 1 – Phần I – Ôn tập – Tiết 5 – 6</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr"/>
@@ -4562,7 +4562,7 @@
       <c r="D136" s="4" t="inlineStr"/>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP VÀ ĐÁNH GIÁ CUỐI HỌC KÌ 1 – PHẦN I – ÔN TẬP – TIẾT 7 – 8</t>
+          <t>Ôn tập và đánh giá cuối học kì 1 – Phần I – Ôn tập – Tiết 7 – 8</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr"/>
@@ -4592,7 +4592,7 @@
       <c r="D137" s="4" t="inlineStr"/>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP VÀ ĐÁNH GIÁ CUỐI HỌC KÌ 1 – PHẦN II – ĐÁNH GIÁ CUỐI HỌC KÌ 1 – TIẾT 9 – 10</t>
+          <t>Ôn tập và đánh giá cuối học kì 1 – Phần II – Đánh giá cuối học kì 1 – Tiết 9 – 10</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -4626,7 +4626,7 @@
       <c r="D138" s="4" t="inlineStr"/>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Bài 1: CHUYỆN BỐN MÙA – TIẾT 1 – 2: ĐỌC: CHUYỆN BỐN MÙA</t>
+          <t>Bài 1: Chuyện bốn mùa – Tiết 1 – 2: Đọc: Chuyện bốn mùa</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -4661,7 +4661,7 @@
       <c r="D139" s="4" t="inlineStr"/>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Bài 1: CHUYỆN BỐN MÙA – TIẾT 3: VIẾT CHỮ HOA Q</t>
+          <t>Bài 1: Chuyện bốn mùa – Tiết 3: Viết chữ hoa Q</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr"/>
@@ -4687,7 +4687,7 @@
       <c r="D140" s="4" t="inlineStr"/>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Bài 1: CHUYỆN BỐN MÙA – TIẾT 4: NÓI VÀ NGHE</t>
+          <t>Bài 1: Chuyện bốn mùa – Tiết 4: Nói và nghe</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr"/>
@@ -4717,7 +4717,7 @@
       <c r="D141" s="4" t="inlineStr"/>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: MÙA NƯỚC NỔI – TIẾT 1 – 2: ĐỌC: MÙA NƯỚC NỔI</t>
+          <t>Bài 2: Mùa nước nổi – Tiết 1 – 2: Đọc: Mùa nước nổi</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       <c r="D142" s="4" t="inlineStr"/>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: MÙA NƯỚC NỔI – TIẾT 3: VIẾT</t>
+          <t>Bài 2: Mùa nước nổi – Tiết 3: Viết</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr"/>
@@ -4782,7 +4782,7 @@
       <c r="D143" s="4" t="inlineStr"/>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: MÙA NƯỚC NỔI – TIẾT 4: LUYỆN TẬP</t>
+          <t>Bài 2: Mùa nước nổi – Tiết 4: Luyện tập</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr"/>
@@ -4808,7 +4808,7 @@
       <c r="D144" s="4" t="inlineStr"/>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: MÙA NƯỚC NỔI – TIẾT 5: VIẾT ĐOẠN VĂN TẢ ĐỒ VẬT</t>
+          <t>Bài 2: Mùa nước nổi – Tiết 5: Viết đoạn văn tả đồ vật</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
       <c r="D145" s="4" t="inlineStr"/>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Bài 2: MÙA NƯỚC NỔI – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 2: Mùa nước nổi – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr"/>
@@ -4865,7 +4865,7 @@
       <c r="D146" s="4" t="inlineStr"/>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Bài 3: HỌA MI HÓT – TIẾT 1 – 2: ĐỌC: HỌA MI HÓT</t>
+          <t>Bài 3: Họa mi hót – Tiết 1 – 2: Đọc: Họa mi hót</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
@@ -4900,7 +4900,7 @@
       <c r="D147" s="4" t="inlineStr"/>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Bài 3: HỌA MI HÓT – TIẾT 3: VIẾT CHỮ HOA R</t>
+          <t>Bài 3: Họa mi hót – Tiết 3: Viết chữ hoa R</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr"/>
@@ -4926,7 +4926,7 @@
       <c r="D148" s="4" t="inlineStr"/>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Bài 3: HỌA MI HÓT – TIẾT 4: NÓI VÀ NGHE</t>
+          <t>Bài 3: Họa mi hót – Tiết 4: Nói và nghe</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr"/>
@@ -4956,7 +4956,7 @@
       <c r="D149" s="4" t="inlineStr"/>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Bài 4: TẾT ĐẾN RỒI – TIẾT 1 – 2: ĐỌC: TẾT ĐẾN RỒI</t>
+          <t>Bài 4: Tết đến rồi – Tiết 1 – 2: Đọc: Tết đến rồi</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -4991,7 +4991,7 @@
       <c r="D150" s="4" t="inlineStr"/>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Bài 4: TẾT ĐẾN RỒI – TIẾT 3: NGHE – VIẾT</t>
+          <t>Bài 4: Tết đến rồi – Tiết 3: Nghe – Viết</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr"/>
@@ -5021,7 +5021,7 @@
       <c r="D151" s="4" t="inlineStr"/>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Bài 4: TẾT ĐẾN RỒI – TIẾT 4: LUYỆN TẬP</t>
+          <t>Bài 4: Tết đến rồi – Tiết 4: Luyện tập</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr"/>
@@ -5047,7 +5047,7 @@
       <c r="D152" s="4" t="inlineStr"/>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Bài 4: TẾT ĐẾN RỒI – TIẾT 5: VIẾT THIỆP CHÚC TẾT</t>
+          <t>Bài 4: Tết đến rồi – Tiết 5: Viết thiệp chúc Tết</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       <c r="D153" s="4" t="inlineStr"/>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Bài 4: TẾT ĐẾN RỒI – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 4: Tết đến rồi – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr"/>
@@ -5104,7 +5104,7 @@
       <c r="D154" s="4" t="inlineStr"/>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Bài 5: GIỌT NƯỚC VÀ BIỂN LỚN – TIẾT 1 – 2: ĐỌC: GIỌT NƯỚC VÀ BIỂN LỚN</t>
+          <t>Bài 5: Giọt nước và biển lớn – Tiết 1 – 2: Đọc: Giọt nước và biển lớn</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -5139,7 +5139,7 @@
       <c r="D155" s="4" t="inlineStr"/>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Bài 5: GIỌT NƯỚC VÀ BIỂN LỚN – TIẾT 3: VIẾT CHỮ HOA S</t>
+          <t>Bài 5: Giọt nước và biển lớn – Tiết 3: Viết chữ hoa S</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr"/>
@@ -5165,7 +5165,7 @@
       <c r="D156" s="4" t="inlineStr"/>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Bài 5: GIỌT NƯỚC VÀ BIỂN LỚN – TIẾT 4: NÓI VÀ NGHE</t>
+          <t>Bài 5: Giọt nước và biển lớn – Tiết 4: Nói và nghe</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr"/>
@@ -5196,7 +5196,7 @@
       <c r="D157" s="4" t="inlineStr"/>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Bài 6: MÙA VÀNG – TIẾT 1 – 2: ĐỌC: MÙA VÀNG</t>
+          <t>Bài 6: Mùa vàng – Tiết 1 – 2: Đọc: Mùa vàng</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
@@ -5232,7 +5232,7 @@
       <c r="D158" s="4" t="inlineStr"/>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Bài 6: MÙA VÀNG – TIẾT 3: VIẾT</t>
+          <t>Bài 6: Mùa vàng – Tiết 3: Viết</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr"/>
@@ -5258,7 +5258,7 @@
       <c r="D159" s="4" t="inlineStr"/>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Bài 6: MÙA VÀNG – TIẾT 4: LUYỆN TẬP</t>
+          <t>Bài 6: Mùa vàng – Tiết 4: Luyện tập</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr"/>
@@ -5288,7 +5288,7 @@
       <c r="D160" s="4" t="inlineStr"/>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Bài 6: MÙA VÀNG – TIẾT 5: VIẾT ĐOẠN VĂN</t>
+          <t>Bài 6: Mùa vàng – Tiết 5: Viết đoạn văn</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       <c r="D161" s="4" t="inlineStr"/>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Bài 6: MÙA VÀNG – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 6: Mùa vàng – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr"/>
@@ -5344,7 +5344,7 @@
       <c r="D162" s="4" t="inlineStr"/>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Bài 7: HẠT THÓC – TIẾT 1 – 2: ĐỌC: HẠT THÓC</t>
+          <t>Bài 7: Hạt thóc – Tiết 1 – 2: Đọc: Hạt thóc</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -5379,7 +5379,7 @@
       <c r="D163" s="4" t="inlineStr"/>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Bài 7: HẠT THÓC – TIẾT 3: VIẾT CHỮ HOA T</t>
+          <t>Bài 7: Hạt thóc – Tiết 3: Viết chữ hoa T</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr"/>
@@ -5405,7 +5405,7 @@
       <c r="D164" s="4" t="inlineStr"/>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Bài 7: HẠT THÓC – TIẾT 4: NÓI VÀ NGHE</t>
+          <t>Bài 7: Hạt thóc – Tiết 4: Nói và nghe</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr"/>
@@ -5436,7 +5436,7 @@
       <c r="D165" s="4" t="inlineStr"/>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Bài 8: LŨY TRE – TIẾT 1 – 2: ĐỌC: LŨY TRE</t>
+          <t>Bài 8: Lũy tre – Tiết 1 – 2: Đọc: Lũy tre</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -5472,7 +5472,7 @@
       <c r="D166" s="4" t="inlineStr"/>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Bài 8: LŨY TRE – TIẾT 3: NGHE – VIẾT</t>
+          <t>Bài 8: Lũy tre – Tiết 3: Nghe – Viết</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr"/>
@@ -5498,7 +5498,7 @@
       <c r="D167" s="4" t="inlineStr"/>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Bài 8: LŨY TRE – TIẾT 4: LUYỆN TẬP</t>
+          <t>Bài 8: Lũy tre – Tiết 4: Luyện tập</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr"/>
@@ -5528,7 +5528,7 @@
       <c r="D168" s="4" t="inlineStr"/>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Bài 8: LŨY TRE – TIẾT 5: VIẾT ĐOẠN VĂN</t>
+          <t>Bài 8: Lũy tre – Tiết 5: Viết đoạn văn</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr"/>
@@ -5554,7 +5554,7 @@
       <c r="D169" s="4" t="inlineStr"/>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Bài 8: LŨY TRE – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 8: Lũy tre – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr"/>
@@ -5584,7 +5584,7 @@
       <c r="D170" s="4" t="inlineStr"/>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Bài 9: VÈ CHIM – TIẾT 1 – 2: ĐỌC – VÈ CHIM</t>
+          <t>Bài 9: Vè chim – Tiết 1 – 2: Đọc – Vè chim</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -5619,7 +5619,7 @@
       <c r="D171" s="4" t="inlineStr"/>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Bài 9: VÈ CHIM – TIẾT 3: VIẾT CHỮ HOA U, Ư</t>
+          <t>Bài 9: Vè chim – Tiết 3: Viết chữ hoa U, Ư</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr"/>
@@ -5645,7 +5645,7 @@
       <c r="D172" s="4" t="inlineStr"/>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Bài 9: VÈ CHIM – TIẾT 4: NÓI VÀ NGHE – CẢM ƠN HỌA MI</t>
+          <t>Bài 9: Vè chim – Tiết 4: Nói và nghe – Cảm ơn họa mi</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr"/>
@@ -5676,7 +5676,7 @@
       <c r="D173" s="4" t="inlineStr"/>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Bài 10: KHỦNG LONG – TIẾT 1 – 2: ĐỌC – KHỦNG LONG</t>
+          <t>Bài 10: Khủng long – Tiết 1 – 2: Đọc – Khủng long</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -5711,7 +5711,7 @@
       <c r="D174" s="4" t="inlineStr"/>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>Bài 10: KHỦNG LONG – TIẾT 3: VIẾT</t>
+          <t>Bài 10: Khủng long – Tiết 3: Viết</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr"/>
@@ -5737,7 +5737,7 @@
       <c r="D175" s="4" t="inlineStr"/>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Bài 10: KHỦNG LONG – TIẾT 4: LUYỆN TẬP</t>
+          <t>Bài 10: Khủng long – Tiết 4: Luyện tập</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr"/>
@@ -5763,7 +5763,7 @@
       <c r="D176" s="4" t="inlineStr"/>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Bài 10: KHỦNG LONG – TIẾT 5 – 6: VIẾT ĐOẠN VĂN – ĐỌC MỞ RỘNG</t>
+          <t>Bài 10: Khủng long – Tiết 5 – 6: Viết đoạn văn – Đọc mở rộng</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr"/>
@@ -5794,7 +5794,7 @@
       <c r="D177" s="4" t="inlineStr"/>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Bài 11: SỰ TÍCH CÂY THÌ LÀ – TIẾT 1 – 2: ĐỌC – SỰ TÍCH CÂY THÌ LÀ</t>
+          <t>Bài 11: Sự tích cây thì là – Tiết 1 – 2: Đọc – Sự tích cây thì là</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -5829,7 +5829,7 @@
       <c r="D178" s="4" t="inlineStr"/>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>Bài 11: SỰ TÍCH CÂY THÌ LÀ – TIẾT 3: VIẾT CHỮ HOA V</t>
+          <t>Bài 11: Sự tích cây thì là – Tiết 3: Viết chữ hoa V</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr"/>
@@ -5855,7 +5855,7 @@
       <c r="D179" s="4" t="inlineStr"/>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Bài 11: SỰ TÍCH CÂY THÌ LÀ – TIẾT 4: NÓI VÀ NGHE – SỰ TÍCH CÂY THÌ LÀ</t>
+          <t>Bài 11: Sự tích cây thì là – Tiết 4: Nói và nghe – Sự tích cây thì là</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr"/>
@@ -5886,7 +5886,7 @@
       <c r="D180" s="4" t="inlineStr"/>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Bài 12: BỜ TRE ĐÓN KHÁCH – TIẾT 1 – 2: ĐỌC – BỜ TRE ĐÓN KHÁCH</t>
+          <t>Bài 12: Bờ tre đón khách – Tiết 1 – 2: Đọc – Bờ tre đón khách</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -5921,7 +5921,7 @@
       <c r="D181" s="4" t="inlineStr"/>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Bài 12: BỜ TRE ĐÓN KHÁCH – TIẾT 3: VIẾT</t>
+          <t>Bài 12: Bờ tre đón khách – Tiết 3: Viết</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr"/>
@@ -5947,7 +5947,7 @@
       <c r="D182" s="4" t="inlineStr"/>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>Bài 12: BỜ TRE ĐÓN KHÁCH – TIẾT 4: LUYỆN TẬP</t>
+          <t>Bài 12: Bờ tre đón khách – Tiết 4: Luyện tập</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr"/>
@@ -5978,7 +5978,7 @@
       <c r="D183" s="4" t="inlineStr"/>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>Bài 12: BỜ TRE ĐÓN KHÁCH – TIẾT 5 – 6: VIẾT ĐOẠN VĂN – ĐỌC MỞ RỘNG</t>
+          <t>Bài 12: Bờ tre đón khách – Tiết 5 – 6: Viết đoạn văn – Đọc mở rộng</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr"/>
@@ -6004,7 +6004,7 @@
       <c r="D184" s="4" t="inlineStr"/>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>Bài 13: TIẾNG CHỔI TRE – TIẾT 1 – 2: ĐỌC – TIẾNG CHỔI TRE</t>
+          <t>Bài 13: Tiếng chổi tre – Tiết 1 – 2: Đọc – Tiếng chổi tre</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -6039,7 +6039,7 @@
       <c r="D185" s="4" t="inlineStr"/>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Bài 13: TIẾNG CHỔI TRE – TIẾT 3: VIẾT CHỮ HOA X</t>
+          <t>Bài 13: Tiếng chổi tre – Tiết 3: Viết chữ hoa X</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr"/>
@@ -6065,7 +6065,7 @@
       <c r="D186" s="4" t="inlineStr"/>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>Bài 13: TIẾNG CHỔI TRE – TIẾT 4: NÓI VÀ NGHE – HẠT GIỐNG NHỎ</t>
+          <t>Bài 13: Tiếng chổi tre – Tiết 4: Nói và nghe – Hạt giống nhỏ</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr"/>
@@ -6095,7 +6095,7 @@
       <c r="D187" s="4" t="inlineStr"/>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Bài 14: CỎ NON CƯỜI RỒI – TIẾT 1 – 2: ĐỌC – CỎ NON CƯỜI RỒI</t>
+          <t>Bài 14: Cỏ non cười rồi – Tiết 1 – 2: Đọc – Cỏ non cười rồi</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
       <c r="D188" s="4" t="inlineStr"/>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>Bài 14: CỎ NON CƯỜI RỒI – TIẾT 3: VIẾT</t>
+          <t>Bài 14: Cỏ non cười rồi – Tiết 3: Viết</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
       <c r="D189" s="4" t="inlineStr"/>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>Bài 14: CỎ NON CƯỜI RỒI – TIẾT 4: LUYỆN TẬP</t>
+          <t>Bài 14: Cỏ non cười rồi – Tiết 4: Luyện tập</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr"/>
@@ -6183,7 +6183,7 @@
       <c r="D190" s="4" t="inlineStr"/>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>Bài 14: CỎ NON CƯỜI RỒI – TIẾT 5 – 6: VIẾT LỜI XIN LỖI – ĐỌC MỞ RỘNG</t>
+          <t>Bài 14: Cỏ non cười rồi – Tiết 5 – 6: Viết lời xin lỗi – Đọc mở rộng</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr"/>
@@ -6213,7 +6213,7 @@
       <c r="D191" s="4" t="inlineStr"/>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>Bài 15: NHỮNG CON SAO BIỂN – TIẾT 1 – 2: ĐỌC – NHỮNG CON SAO BIỂN</t>
+          <t>Bài 15: Những con sao biển – Tiết 1 – 2: Đọc – Những con sao biển</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -6249,7 +6249,7 @@
       <c r="D192" s="4" t="inlineStr"/>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>Bài 15: NHỮNG CON SAO BIỂN – TIẾT 3: VIẾT CHỮ HOA Y</t>
+          <t>Bài 15: Những con sao biển – Tiết 3: Viết chữ hoa Y</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr"/>
@@ -6275,7 +6275,7 @@
       <c r="D193" s="4" t="inlineStr"/>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Bài 15: NHỮNG CON SAO BIỂN – TIẾT 4: NÓI VÀ NGHE – BẢO VỆ MÔI TRƯỜNG</t>
+          <t>Bài 15: Những con sao biển – Tiết 4: Nói và nghe – Bảo vệ môi trường</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr"/>
@@ -6305,7 +6305,7 @@
       <c r="D194" s="4" t="inlineStr"/>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>Bài 16: TẠM BIỆT CÁNH CAM – TIẾT 1 – 2: ĐỌC – TẠM BIỆT CÁNH CAM</t>
+          <t>Bài 16: Tạm biệt cánh cam – Tiết 1 – 2: Đọc – Tạm biệt cánh cam</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -6341,7 +6341,7 @@
       <c r="D195" s="4" t="inlineStr"/>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>Bài 16: TẠM BIỆT CÁNH CAM – TIẾT 3: VIẾT</t>
+          <t>Bài 16: Tạm biệt cánh cam – Tiết 3: Viết</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr"/>
@@ -6367,7 +6367,7 @@
       <c r="D196" s="4" t="inlineStr"/>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>Bài 16: TẠM BIỆT CÁNH CAM – TIẾT 4: LUYỆN TẬP</t>
+          <t>Bài 16: Tạm biệt cánh cam – Tiết 4: Luyện tập</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr"/>
@@ -6393,7 +6393,7 @@
       <c r="D197" s="4" t="inlineStr"/>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>Bài 16: TẠM BIỆT CÁNH CAM – TIẾT 5 – 6: VIẾT ĐOẠN – ĐỌC MỞ RỘNG</t>
+          <t>Bài 16: Tạm biệt cánh cam – Tiết 5 – 6: Viết đoạn – Đọc mở rộng</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr"/>
@@ -6424,7 +6424,7 @@
       <c r="D198" s="4" t="inlineStr"/>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>Bài: ÔN TẬP GIỮA HỌC KÌ II – TIẾT 1 - 2: ÔN TẬP</t>
+          <t>Bài: Ôn tập giữa học kì II – Tiết 1 - 2: Ôn tập</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -6458,7 +6458,7 @@
       <c r="D199" s="4" t="inlineStr"/>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>Bài: ÔN TẬP GIỮA HỌC KÌ II – TIẾT 3 - 4: ÔN TẬP</t>
+          <t>Bài: Ôn tập giữa học kì II – Tiết 3 - 4: Ôn tập</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr"/>
@@ -6488,7 +6488,7 @@
       <c r="D200" s="4" t="inlineStr"/>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>Bài: ÔN TẬP GIỮA HỌC KÌ II – TIẾT 5 - 6: ÔN TẬP</t>
+          <t>Bài: Ôn tập giữa học kì II – Tiết 5 - 6: Ôn tập</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       <c r="D201" s="4" t="inlineStr"/>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>Bài: ÔN TẬP GIỮA HỌC KÌ II – TIẾT 7 - 8: ÔN TẬP</t>
+          <t>Bài: Ôn tập giữa học kì II – Tiết 7 - 8: Ôn tập</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr"/>
@@ -6548,7 +6548,7 @@
       <c r="D202" s="4" t="inlineStr"/>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>Bài: ÔN TẬP GIỮA HỌC KÌ II – TIẾT 9 - 10: ÔN TẬP</t>
+          <t>Bài: Ôn tập giữa học kì II – Tiết 9 - 10: Ôn tập</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr"/>
@@ -6578,7 +6578,7 @@
       <c r="D203" s="4" t="inlineStr"/>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>Bài 17: NHỮNG CÁCH CHÀO ĐỘC ĐÁO – TIẾT 1 - 2: ĐỌC - NHỮNG CÁCH CHÀO ĐỘC ĐÁO</t>
+          <t>Bài 17: Những cách chào độc đáo – Tiết 1 - 2: Đọc - Những cách chào độc đáo</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -6613,7 +6613,7 @@
       <c r="D204" s="4" t="inlineStr"/>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>Bài 17: NHỮNG CÁCH CHÀO ĐỘC ĐÁO – TIẾT 3: VIẾT - CHỮ HOA A (KIỂU 2)</t>
+          <t>Bài 17: Những cách chào độc đáo – Tiết 3: Viết - Chữ hoa A (kiểu 2)</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       <c r="D205" s="4" t="inlineStr"/>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>Bài 17: NHỮNG CÁCH CHÀO ĐỘC ĐÁO – TIẾT 4: NÓI VÀ NGHE - LỚP HỌC VIẾT THƯ</t>
+          <t>Bài 17: Những cách chào độc đáo – Tiết 4: Nói và nghe - Lớp học viết thư</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr"/>
@@ -6669,7 +6669,7 @@
       <c r="D206" s="4" t="inlineStr"/>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Bài 18: THƯ VIỆN BIẾT ĐI – TIẾT 1 - 2: ĐỌC - THƯ VIỆN BIẾT ĐI</t>
+          <t>Bài 18: Thư viện biết đi – Tiết 1 - 2: Đọc - Thư viện biết đi</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -6704,7 +6704,7 @@
       <c r="D207" s="4" t="inlineStr"/>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Bài 18: THƯ VIỆN BIẾT ĐI – TIẾT 3: VIẾT - NGHE - VIẾT: THƯ VIỆN BIẾT ĐI – TIẾT 4: LUYỆN TỪ VÀ CÂU – TIẾT 5 - 6: LUYỆN VIẾT ĐOẠN - ĐỌC MỞ RỘNG</t>
+          <t>Bài 18: Thư viện biết đi – Tiết 3: Viết - Nghe - Viết: Thư viện biết đi – Tiết 4: Luyện từ và câu – Tiết 5 - 6: Luyện viết đoạn - Đọc mở rộng</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr"/>
@@ -6735,7 +6735,7 @@
       <c r="D208" s="4" t="inlineStr"/>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>Bài 19: CẢM ƠN ANH HÀ MÃ – TIẾT 1 - 2: ĐỌC - CẢM ƠN ANH HÀ MÃ</t>
+          <t>Bài 19: Cảm ơn anh hà mã – Tiết 1 - 2: Đọc - Cảm ơn anh hà mã</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
@@ -6769,7 +6769,7 @@
       <c r="D209" s="4" t="inlineStr"/>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Bài 19: CẢM ƠN ANH HÀ MÃ – TIẾT 3: VIẾT - CHỮ HOA M (kiểu 2)</t>
+          <t>Bài 19: Cảm ơn anh hà mã – Tiết 3: Viết - Chữ hoa M (kiểu 2)</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr"/>
@@ -6795,7 +6795,7 @@
       <c r="D210" s="4" t="inlineStr"/>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>Bài 19: CẢM ƠN ANH HÀ MÃ – TIẾT 4: NÓI VÀ NGHE - KỂ CHUYỆN CẢM ƠN ANH HÀ MÃ</t>
+          <t>Bài 19: Cảm ơn anh hà mã – Tiết 4: Nói và nghe - Kể chuyện cảm ơn anh hà mã</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr"/>
@@ -6825,7 +6825,7 @@
       <c r="D211" s="4" t="inlineStr"/>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>Bài 20: TỪ CHÚ BỒ CÂU ĐẾN IN-TƠ-NÉT – TIẾT 1 - 2: ĐỌC - TỪ CHÚ BỒ CÂU ĐẾN IN-TƠ-NÉT</t>
+          <t>Bài 20: Từ chú bồ câu đến in-tơ-nét – Tiết 1 - 2: Đọc - Từ chú bồ câu đến in-tơ-nét</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
@@ -6861,7 +6861,7 @@
       <c r="D212" s="4" t="inlineStr"/>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>Bài 20: TỪ CHÚ BỒ CÂU ĐẾN IN-TƠ-NÉT – TIẾT 3: VIẾT - NGHE VIẾT; PHÂN BIỆT EO/OE, L/N, ÊN/ÊNH</t>
+          <t>Bài 20: Từ chú bồ câu đến in-tơ-nét – Tiết 3: Viết - Nghe viết; phân biệt eo/oe, L/N, ên/ênh</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr"/>
@@ -6891,7 +6891,7 @@
       <c r="D213" s="4" t="inlineStr"/>
       <c r="E213" s="4" t="inlineStr">
         <is>
-          <t>Bài 20: TỪ CHÚ BỒ CÂU ĐẾN IN-TƠ-NÉT – TIẾT 4: LUYỆN TỪ VÀ CÂU - MỞ RỘNG VỐN TỪ VỀ GIAO TIẾP, KẾT NỐI; DẤU CÂU</t>
+          <t>Bài 20: Từ chú bồ câu đến in-tơ-nét – Tiết 4: Luyện từ và câu - Mở rộng vốn từ về giao tiếp, kết nối; dấu câu</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr"/>
@@ -6921,7 +6921,7 @@
       <c r="D214" s="4" t="inlineStr"/>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>Bài 20: TỪ CHÚ BỒ CÂU ĐẾN IN-TƠ-NÉT – TIẾT 5: VIẾT ĐOẠN VĂN TẢ MỘT ĐỒ DÙNG TRONG GIA ĐÌNH</t>
+          <t>Bài 20: Từ chú bồ câu đến in-tơ-nét – Tiết 5: Viết đoạn văn tả một đồ dùng trong gia đình</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr"/>
@@ -6947,7 +6947,7 @@
       <c r="D215" s="4" t="inlineStr"/>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>Bài 20: TỪ CHÚ BỒ CÂU ĐẾN IN-TƠ-NÉT – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 20: Từ chú bồ câu đến in-tơ-nét – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr"/>
@@ -6978,7 +6978,7 @@
       <c r="D216" s="4" t="inlineStr"/>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>Bài 21: MAI AN TIÊM – TIẾT 1 - 2: ĐỌC - MAI AN TIÊM</t>
+          <t>Bài 21: Mai An Tiêm – Tiết 1 - 2: Đọc - Mai An Tiêm</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
@@ -7014,7 +7014,7 @@
       <c r="D217" s="4" t="inlineStr"/>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>Bài 21: MAI AN TIÊM – TIẾT 3: VIẾT - CHỮ HOA N (kiểu 2)</t>
+          <t>Bài 21: Mai An Tiêm – Tiết 3: Viết - Chữ hoa N (kiểu 2)</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr"/>
@@ -7040,7 +7040,7 @@
       <c r="D218" s="4" t="inlineStr"/>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>Bài 21: MAI AN TIÊM – TIẾT 4: NÓI VÀ NGHE - KỂ CHUYỆN MAI AN TIÊM</t>
+          <t>Bài 21: Mai An Tiêm – Tiết 4: Nói và nghe - Kể chuyện Mai An Tiêm</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr"/>
@@ -7070,7 +7070,7 @@
       <c r="D219" s="4" t="inlineStr"/>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>Bài 22: THƯ GỬI BỐ NGOÀI ĐẢO – TIẾT 1 - 2: ĐỌC - THƯ GỬI BỐ NGOÀI ĐẢO</t>
+          <t>Bài 22: Thư gửi bố ngoài đảo – Tiết 1 - 2: Đọc - Thư gửi bố ngoài đảo</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
@@ -7105,7 +7105,7 @@
       <c r="D220" s="4" t="inlineStr"/>
       <c r="E220" s="4" t="inlineStr">
         <is>
-          <t>Bài 22: THƯ GỬI BỐ NGOÀI ĐẢO – TIẾT 3: VIẾT - NGHE VIẾT; PHÂN BIỆT D/GI, S/X, IP/IÊP</t>
+          <t>Bài 22: Thư gửi bố ngoài đảo – Tiết 3: Viết - Nghe viết; phân biệt d/gi, S/X, ip/iêp</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr"/>
@@ -7131,7 +7131,7 @@
       <c r="D221" s="4" t="inlineStr"/>
       <c r="E221" s="4" t="inlineStr">
         <is>
-          <t>Bài 22: THƯ GỬI BỐ NGOÀI ĐẢO – TIẾT 4: LUYỆN TỪ VÀ CÂU - MỞ RỘNG VỐN TỪ VỀ NGƯỜI LÀM VIỆC TRÊN BIỂN; CÂU NÊU HOẠT ĐỘNG</t>
+          <t>Bài 22: Thư gửi bố ngoài đảo – Tiết 4: Luyện từ và câu - Mở rộng vốn từ về người làm việc trên biển; câu nêu hoạt động</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr"/>
@@ -7161,7 +7161,7 @@
       <c r="D222" s="4" t="inlineStr"/>
       <c r="E222" s="4" t="inlineStr">
         <is>
-          <t>Bài 22: THƯ GỬI BỐ NGOÀI ĐẢO – TIẾT 5: VIẾT LỜI CẢM ƠN CÁC CHÚ BỘ ĐỘI HẢI QUÂN</t>
+          <t>Bài 22: Thư gửi bố ngoài đảo – Tiết 5: Viết lời cảm ơn các chú bộ đội hải quân</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr"/>
@@ -7187,7 +7187,7 @@
       <c r="D223" s="4" t="inlineStr"/>
       <c r="E223" s="4" t="inlineStr">
         <is>
-          <t>Bài 22: THƯ GỬI BỐ NGOÀI ĐẢO – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 22: Thư gửi bố ngoài đảo – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr"/>
@@ -7217,7 +7217,7 @@
       <c r="D224" s="4" t="inlineStr"/>
       <c r="E224" s="4" t="inlineStr">
         <is>
-          <t>Bài 23: BÓP NÁT QUẢ CAM – TIẾT 1 - 2: ĐỌC - BÓP NÁT QUẢ CAM</t>
+          <t>Bài 23: Bóp nát quả cam – Tiết 1 - 2: Đọc - Bóp nát quả cam</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
@@ -7252,7 +7252,7 @@
       <c r="D225" s="4" t="inlineStr"/>
       <c r="E225" s="4" t="inlineStr">
         <is>
-          <t>Bài 23: BÓP NÁT QUẢ CAM – TIẾT 3: VIẾT - CHỮ HOA Q (KIỂU 2)</t>
+          <t>Bài 23: Bóp nát quả cam – Tiết 3: Viết - Chữ hoa Q (kiểu 2)</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr"/>
@@ -7278,7 +7278,7 @@
       <c r="D226" s="4" t="inlineStr"/>
       <c r="E226" s="4" t="inlineStr">
         <is>
-          <t>Bài 23: BÓP NÁT QUẢ CAM – TIẾT 4: NÓI VÀ NGHE - KỂ CHUYỆN BÓP NÁT QUẢ CAM</t>
+          <t>Bài 23: Bóp nát quả cam – Tiết 4: Nói và nghe - Kể chuyện bóp nát quả cam</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr"/>
@@ -7309,7 +7309,7 @@
       <c r="D227" s="4" t="inlineStr"/>
       <c r="E227" s="4" t="inlineStr">
         <is>
-          <t>Bài 24: CHIẾC RỄ ĐA TRÒN – TIẾT 1 - 2: ĐỌC - CHIẾC RỄ ĐA TRÒN</t>
+          <t>Bài 24: Chiếc rễ đa tròn – Tiết 1 - 2: Đọc - Chiếc rễ đa tròn</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -7345,7 +7345,7 @@
       <c r="D228" s="4" t="inlineStr"/>
       <c r="E228" s="4" t="inlineStr">
         <is>
-          <t>Bài 24: CHIẾC RỄ ĐA TRÒN – TIẾT 3: VIẾT - NGHE VIẾT; VIẾT HOA TÊN NGƯỜI; PHÂN BIỆT IU/ƯU, IM/IÊM</t>
+          <t>Bài 24: Chiếc rễ đa tròn – Tiết 3: Viết - Nghe viết; viết hoa tên người; phân biệt iu/ưu, im/iêm</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr"/>
@@ -7371,7 +7371,7 @@
       <c r="D229" s="4" t="inlineStr"/>
       <c r="E229" s="4" t="inlineStr">
         <is>
-          <t>Bài 24: CHIẾC RỄ ĐA TRÒN – TIẾT 4: LUYỆN TỪ VÀ CÂU - MỞ RỘNG VỐN TỪ VỀ BÁC HỒ VÀ NHÂN DÂN</t>
+          <t>Bài 24: Chiếc rễ đa tròn – Tiết 4: Luyện từ và câu - Mở rộng vốn từ về Bác Hồ và nhân dân</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
       <c r="D230" s="4" t="inlineStr"/>
       <c r="E230" s="4" t="inlineStr">
         <is>
-          <t>Bài 24: CHIẾC RỄ ĐA TRÒN – TIẾT 5: VIẾT ĐOẠN VĂN KỂ MỘT SỰ VIỆC</t>
+          <t>Bài 24: Chiếc rễ đa tròn – Tiết 5: Viết đoạn văn kể một sự việc</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr"/>
@@ -7431,7 +7431,7 @@
       <c r="D231" s="4" t="inlineStr"/>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>Bài 24: CHIẾC RỄ ĐA TRÒN – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 24: Chiếc rễ đa tròn – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr"/>
@@ -7461,7 +7461,7 @@
       <c r="D232" s="4" t="inlineStr"/>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>Bài 25: ĐẤT NƯỚC CHÚNG MÌNH – TIẾT 1 - 2: ĐỌC - ĐẤT NƯỚC CHÚNG MÌNH</t>
+          <t>Bài 25: Đất nước chúng mình – Tiết 1 - 2: Đọc - Đất nước chúng mình</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
@@ -7496,7 +7496,7 @@
       <c r="D233" s="4" t="inlineStr"/>
       <c r="E233" s="4" t="inlineStr">
         <is>
-          <t>Bài 25: ĐẤT NƯỚC CHÚNG MÌNH – TIẾT 3: VIẾT - CHỮ HOA V (KIỂU 2)</t>
+          <t>Bài 25: Đất nước chúng mình – Tiết 3: Viết - Chữ hoa V (kiểu 2)</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       <c r="D234" s="4" t="inlineStr"/>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>Bài 25: ĐẤT NƯỚC CHÚNG MÌNH – TIẾT 4: NÓI VÀ NGHE - KỂ CHUYỆN THÁNH GIÓNG</t>
+          <t>Bài 25: Đất nước chúng mình – Tiết 4: Nói và nghe - Kể chuyện Thánh Gióng</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       <c r="D235" s="4" t="inlineStr"/>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>Bài 26: TRÊN CÁC MIỀN ĐẤT NƯỚC – TIẾT 1 - 2: ĐỌC - TRÊN CÁC MIỀN ĐẤT NƯỚC</t>
+          <t>Bài 26: Trên các miền đất nước – Tiết 1 - 2: Đọc - Trên các miền đất nước</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
@@ -7591,7 +7591,7 @@
       <c r="D236" s="4" t="inlineStr"/>
       <c r="E236" s="4" t="inlineStr">
         <is>
-          <t>Bài 26: TRÊN CÁC MIỀN ĐẤT NƯỚC – TIẾT 3: VIẾT - NGHE VIẾT; VIẾT HOA TÊN ĐỊA LÍ; PHÂN BIỆT CH/TR, IU/IÊU</t>
+          <t>Bài 26: Trên các miền đất nước – Tiết 3: Viết - Nghe viết; viết hoa tên địa lí; phân biệt CH/TR, iu/iêu</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr"/>
@@ -7617,7 +7617,7 @@
       <c r="D237" s="4" t="inlineStr"/>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>Bài 26: TRÊN CÁC MIỀN ĐẤT NƯỚC – TIẾT 4: LUYỆN TỪ VÀ CÂU - MỞ RỘNG VỐN TỪ VỀ SẢN PHẨM TRUYỀN THỐNG; CÂU GIỚI THIỆU</t>
+          <t>Bài 26: Trên các miền đất nước – Tiết 4: Luyện từ và câu - Mở rộng vốn từ về sản phẩm truyền thống; câu giới thiệu</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr"/>
@@ -7647,7 +7647,7 @@
       <c r="D238" s="4" t="inlineStr"/>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>Bài 26: TRÊN CÁC MIỀN ĐẤT NƯỚC – TIẾT 5: VIẾT ĐOẠN VĂN GIỚI THIỆU ĐỒ VẬT LÀM TỪ TRE/GỖ</t>
+          <t>Bài 26: Trên các miền đất nước – Tiết 5: Viết đoạn văn giới thiệu đồ vật làm từ tre/gỗ</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr"/>
@@ -7673,7 +7673,7 @@
       <c r="D239" s="4" t="inlineStr"/>
       <c r="E239" s="4" t="inlineStr">
         <is>
-          <t>Bài 26: TRÊN CÁC MIỀN ĐẤT NƯỚC – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 26: Trên các miền đất nước – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr"/>
@@ -7703,7 +7703,7 @@
       <c r="D240" s="4" t="inlineStr"/>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>Bài 27: CHUYỆN QUẢ BẦU – TIẾT 1 - 2: ĐỌC - CHUYỆN QUẢ BẦU</t>
+          <t>Bài 27: Chuyện quả bầu – Tiết 1 - 2: Đọc - Chuyện quả bầu</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
@@ -7738,7 +7738,7 @@
       <c r="D241" s="4" t="inlineStr"/>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>Bài 27: CHUYỆN QUẢ BẦU – TIẾT 3: VIẾT - ÔN CHỮ HOA A, M, N (KIỂU 2)</t>
+          <t>Bài 27: Chuyện quả bầu – Tiết 3: Viết - Ôn chữ hoa A, M, N (kiểu 2)</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr"/>
@@ -7764,7 +7764,7 @@
       <c r="D242" s="4" t="inlineStr"/>
       <c r="E242" s="4" t="inlineStr">
         <is>
-          <t>Bài 27: CHUYỆN QUẢ BẦU – TIẾT 4: NÓI VÀ NGHE - KỂ CHUYỆN CHUYỆN QUẢ BẦU</t>
+          <t>Bài 27: Chuyện quả bầu – Tiết 4: Nói và nghe - Kể chuyện chuyện quả bầu</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr"/>
@@ -7795,7 +7795,7 @@
       <c r="D243" s="4" t="inlineStr"/>
       <c r="E243" s="4" t="inlineStr">
         <is>
-          <t>Bài 28: KHÁM PHÁ ĐÁY BIỂN Ở TRƯỜNG SA – TIẾT 1 - 2: ĐỌC - KHÁM PHÁ ĐÁY BIỂN Ở TRƯỜNG SA</t>
+          <t>Bài 28: Khám phá đáy biển ở Trường Sa – Tiết 1 - 2: Đọc - Khám phá đáy biển ở Trường Sa</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
@@ -7830,7 +7830,7 @@
       <c r="D244" s="4" t="inlineStr"/>
       <c r="E244" s="4" t="inlineStr">
         <is>
-          <t>Bài 28: KHÁM PHÁ ĐÁY BIỂN Ở TRƯỜNG SA – TIẾT 3: VIẾT - NGHE VIẾT; PHÂN BIỆT IT/UYT, IÊU/ƯƠU, IN/INH</t>
+          <t>Bài 28: Khám phá đáy biển ở Trường Sa – Tiết 3: Viết - Nghe viết; phân biệt it/uyt, iêu/ươu, in/inh</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
       <c r="D245" s="4" t="inlineStr"/>
       <c r="E245" s="4" t="inlineStr">
         <is>
-          <t>Bài 28: KHÁM PHÁ ĐÁY BIỂN Ở TRƯỜNG SA – TIẾT 4: LUYỆN TỪ VÀ CÂU - MỞ RỘNG VỐN TỪ VỀ CÁC LOÀI VẬT DƯỚI BIỂN; DẤU CHẤM, DẤU PHẨY</t>
+          <t>Bài 28: Khám phá đáy biển ở Trường Sa – Tiết 4: Luyện từ và câu - Mở rộng vốn từ về các loài vật dưới biển; dấu chấm, dấu phẩy</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr"/>
@@ -7887,7 +7887,7 @@
       <c r="D246" s="4" t="inlineStr"/>
       <c r="E246" s="4" t="inlineStr">
         <is>
-          <t>Bài 28: KHÁM PHÁ ĐÁY BIỂN Ở TRƯỜNG SA – TIẾT 5: VIẾT ĐOẠN VĂN KỂ VỀ MỘT BUỔI ĐI CHƠI</t>
+          <t>Bài 28: Khám phá đáy biển ở Trường Sa – Tiết 5: Viết đoạn văn kể về một buổi đi chơi</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr"/>
@@ -7913,7 +7913,7 @@
       <c r="D247" s="4" t="inlineStr"/>
       <c r="E247" s="4" t="inlineStr">
         <is>
-          <t>Bài 28: KHÁM PHÁ ĐÁY BIỂN Ở TRƯỜNG SA – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 28: Khám phá đáy biển ở Trường Sa – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr"/>
@@ -7943,7 +7943,7 @@
       <c r="D248" s="4" t="inlineStr"/>
       <c r="E248" s="4" t="inlineStr">
         <is>
-          <t>Bài 29: HỒ GƯƠM – TIẾT 1 - 2: ĐỌC - HỒ GƯƠM</t>
+          <t>Bài 29: Hồ Gươm – Tiết 1 - 2: Đọc - Hồ Gươm</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
@@ -7979,7 +7979,7 @@
       <c r="D249" s="4" t="inlineStr"/>
       <c r="E249" s="4" t="inlineStr">
         <is>
-          <t>Bài 29: HỒ GƯƠM – TIẾT 3: VIẾT - ÔN CHỮ HOA Q, V (KIỂU 2)</t>
+          <t>Bài 29: Hồ Gươm – Tiết 3: Viết - Ôn chữ hoa Q, V (kiểu 2)</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr"/>
@@ -8005,7 +8005,7 @@
       <c r="D250" s="4" t="inlineStr"/>
       <c r="E250" s="4" t="inlineStr">
         <is>
-          <t>Bài 29: HỒ GƯƠM – TIẾT 4: NÓI VÀ NGHE - NÓI VỀ QUÊ HƯƠNG, ĐẤT NƯỚC EM</t>
+          <t>Bài 29: Hồ Gươm – Tiết 4: Nói và nghe - Nói về quê hương, đất nước em</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr"/>
@@ -8036,7 +8036,7 @@
       <c r="D251" s="4" t="inlineStr"/>
       <c r="E251" s="4" t="inlineStr">
         <is>
-          <t>Bài 30: CÁNH ĐỒNG QUÊ EM – TIẾT 1 - 2: ĐỌC - CÁNH ĐỒNG QUÊ EM</t>
+          <t>Bài 30: Cánh đồng quê em – Tiết 1 - 2: Đọc - Cánh đồng quê em</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
@@ -8072,7 +8072,7 @@
       <c r="D252" s="4" t="inlineStr"/>
       <c r="E252" s="4" t="inlineStr">
         <is>
-          <t>Bài 30: CÁNH ĐỒNG QUÊ EM – TIẾT 3: VIẾT - NGHE VIẾT; VIẾT HOA TÊN RIÊNG ĐỊA LÍ; PHÂN BIỆT R/D/GI, DẤU HỎI/DẤU NGÃ</t>
+          <t>Bài 30: Cánh đồng quê em – Tiết 3: Viết - Nghe viết; viết hoa tên riêng địa lí; phân biệt r/d/gi, dấu hỏi/dấu ngã</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr"/>
@@ -8098,7 +8098,7 @@
       <c r="D253" s="4" t="inlineStr"/>
       <c r="E253" s="4" t="inlineStr">
         <is>
-          <t>Bài 30: CÁNH ĐỒNG QUÊ EM – TIẾT 4: LUYỆN TỪ VÀ CÂU - MỞ RỘNG VỐN TỪ VỀ NGHỀ NGHIỆP; CÂU NÊU HOẠT ĐỘNG, CÔNG VIỆC</t>
+          <t>Bài 30: Cánh đồng quê em – Tiết 4: Luyện từ và câu - Mở rộng vốn từ về nghề nghiệp; câu nêu hoạt động, công việc</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr"/>
@@ -8129,7 +8129,7 @@
       <c r="D254" s="4" t="inlineStr"/>
       <c r="E254" s="4" t="inlineStr">
         <is>
-          <t>Bài 30: CÁNH ĐỒNG QUÊ EM – TIẾT 5: VIẾT ĐOẠN VĂN KỂ VỀ CÔNG VIỆC CỦA MỘT NGƯỜI</t>
+          <t>Bài 30: Cánh đồng quê em – Tiết 5: Viết đoạn văn kể về công việc của một người</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr"/>
@@ -8160,7 +8160,7 @@
       <c r="D255" s="4" t="inlineStr"/>
       <c r="E255" s="4" t="inlineStr">
         <is>
-          <t>Bài 30: CÁNH ĐỒNG QUÊ EM – TIẾT 6: ĐỌC MỞ RỘNG</t>
+          <t>Bài 30: Cánh đồng quê em – Tiết 6: Đọc mở rộng</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr"/>
@@ -8190,7 +8190,7 @@
       <c r="D256" s="4" t="inlineStr"/>
       <c r="E256" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP VÀ ĐÁNH GIÁ CUỐI HỌC KÌ 2 – PHẦN I - ÔN TẬP – TIẾT 1 - 2</t>
+          <t>Ôn tập và đánh giá cuối học kì 2 – Phần I - Ôn tập – Tiết 1 - 2</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
@@ -8224,7 +8224,7 @@
       <c r="D257" s="4" t="inlineStr"/>
       <c r="E257" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP VÀ ĐÁNH GIÁ CUỐI HỌC KÌ 2 – PHẦN I - ÔN TẬP – TIẾT 3 - 4</t>
+          <t>Ôn tập và đánh giá cuối học kì 2 – Phần I - Ôn tập – Tiết 3 - 4</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr"/>
@@ -8254,7 +8254,7 @@
       <c r="D258" s="4" t="inlineStr"/>
       <c r="E258" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP VÀ ĐÁNH GIÁ CUỐI HỌC KÌ 2 – PHẦN I - ÔN TẬP – TIẾT 5 - 6</t>
+          <t>Ôn tập và đánh giá cuối học kì 2 – Phần I - Ôn tập – Tiết 5 - 6</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr"/>
@@ -8284,7 +8284,7 @@
       <c r="D259" s="4" t="inlineStr"/>
       <c r="E259" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP VÀ ĐÁNH GIÁ CUỐI HỌC KÌ 2 – PHẦN I - ÔN TẬP – TIẾT 7 - 8</t>
+          <t>Ôn tập và đánh giá cuối học kì 2 – Phần I - Ôn tập – Tiết 7 - 8</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr"/>
@@ -8314,7 +8314,7 @@
       <c r="D260" s="4" t="inlineStr"/>
       <c r="E260" s="4" t="inlineStr">
         <is>
-          <t>ÔN TẬP VÀ ĐÁNH GIÁ CUỐI HỌC KÌ 2 – PHẦN II - ĐÁNH GIÁ CUỐI HỌC KÌ 2 – TIẾT 9 - 10</t>
+          <t>Ôn tập và đánh giá cuối học kì 2 – Phần II - Đánh giá cuối học kì 2 – Tiết 9 - 10</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: SẮC MÀU ÂM THANH</t>
+          <t>Chủ đề 1: Sắc màu âm thanh</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: SẮC MÀU ÂM THANH</t>
+          <t>Chủ đề 1: Sắc màu âm thanh</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: SẮC MÀU ÂM THANH</t>
+          <t>Chủ đề 1: Sắc màu âm thanh</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -17729,7 +17729,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: SẮC MÀU ÂM THANH</t>
+          <t>Chủ đề 1: Sắc màu âm thanh</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: EM YÊU LÀN ĐIỆU DÂN CA</t>
+          <t>Chủ đề 2: Em yêu làn điệu dân ca</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -17793,7 +17793,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: EM YÊU LÀN ĐIỆU DÂN CA</t>
+          <t>Chủ đề 2: Em yêu làn điệu dân ca</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -17827,7 +17827,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: EM YÊU LÀN ĐIỆU DÂN CA</t>
+          <t>Chủ đề 2: Em yêu làn điệu dân ca</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -17862,7 +17862,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: EM YÊU LÀN ĐIỆU DÂN CA</t>
+          <t>Chủ đề 2: Em yêu làn điệu dân ca</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -17898,7 +17898,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: MÁI TRƯỜNG THÂN YÊU</t>
+          <t>Chủ đề 3: Mái trường thân yêu</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -17932,7 +17932,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: MÁI TRƯỜNG THÂN YÊU</t>
+          <t>Chủ đề 3: Mái trường thân yêu</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: MÁI TRƯỜNG THÂN YÊU</t>
+          <t>Chủ đề 3: Mái trường thân yêu</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: MÁI TRƯỜNG THÂN YÊU</t>
+          <t>Chủ đề 3: Mái trường thân yêu</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -18030,7 +18030,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: TUỔI THƠ</t>
+          <t>Chủ đề 4: Tuổi thơ</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -18064,7 +18064,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: TUỔI THƠ</t>
+          <t>Chủ đề 4: Tuổi thơ</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: TUỔI THƠ</t>
+          <t>Chủ đề 4: Tuổi thơ</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -18133,7 +18133,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: TUỔI THƠ</t>
+          <t>Chủ đề 4: Tuổi thơ</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -18163,7 +18163,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: TUỔI THƠ</t>
+          <t>Chủ đề 4: Tuổi thơ</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: TUỔI THƠ</t>
+          <t>Chủ đề 4: Tuổi thơ</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: MÙA XUÂN</t>
+          <t>Chủ đề 5: Mùa xuân</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -18261,7 +18261,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: MÙA XUÂN</t>
+          <t>Chủ đề 5: Mùa xuân</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: MÙA XUÂN</t>
+          <t>Chủ đề 5: Mùa xuân</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -18329,7 +18329,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: MÙA XUÂN</t>
+          <t>Chủ đề 5: Mùa xuân</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: GIA ĐÌNH YÊU THƯƠNG</t>
+          <t>Chủ đề 6: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -18393,7 +18393,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: GIA ĐÌNH YÊU THƯƠNG</t>
+          <t>Chủ đề 6: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -18427,7 +18427,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: GIA ĐÌNH YÊU THƯƠNG</t>
+          <t>Chủ đề 6: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -18462,7 +18462,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: GIA ĐÌNH YÊU THƯƠNG</t>
+          <t>Chủ đề 6: Gia đình yêu thương</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: NHỮNG CON VẬT QUANH EM</t>
+          <t>Chủ đề 7: Những con vật quanh em</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -18532,7 +18532,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: NHỮNG CON VẬT QUANH EM</t>
+          <t>Chủ đề 7: Những con vật quanh em</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: NHỮNG CON VẬT QUANH EM</t>
+          <t>Chủ đề 7: Những con vật quanh em</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 7: NHỮNG CON VẬT QUANH EM</t>
+          <t>Chủ đề 7: Những con vật quanh em</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -18630,7 +18630,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: MÙA HÈ VUI</t>
+          <t>Chủ đề 8: Mùa hè vui</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -18664,7 +18664,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: MÙA HÈ VUI</t>
+          <t>Chủ đề 8: Mùa hè vui</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -18694,7 +18694,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: MÙA HÈ VUI</t>
+          <t>Chủ đề 8: Mùa hè vui</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -18728,7 +18728,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: MÙA HÈ VUI</t>
+          <t>Chủ đề 8: Mùa hè vui</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 8: MÙA HÈ VUI</t>
+          <t>Chủ đề 8: Mùa hè vui</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -22465,7 +22465,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -22536,7 +22536,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -22571,7 +22571,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -22601,7 +22601,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -22700,7 +22700,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -22873,7 +22873,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -22903,7 +22903,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -22937,7 +22937,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -22972,7 +22972,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -23006,7 +23006,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -23040,7 +23040,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KHÁM PHÁ BẢN THÂN</t>
+          <t>Chủ đề: Khám phá bản thân</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -24208,7 +24208,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIA ĐÌNH THÂN THƯƠNG</t>
+          <t>Chủ đề: Gia đình thân thương</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -24242,7 +24242,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIA ĐÌNH THÂN THƯƠNG</t>
+          <t>Chủ đề: Gia đình thân thương</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -24277,7 +24277,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: GIA ĐÌNH THÂN THƯƠNG</t>
+          <t>Chủ đề: Gia đình thân thương</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -25241,7 +25241,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -25311,7 +25311,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -25346,7 +25346,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -25416,7 +25416,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -25451,7 +25451,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -25485,7 +25485,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -25519,7 +25519,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -25555,7 +25555,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -25590,7 +25590,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -25625,7 +25625,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -25660,7 +25660,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -25695,7 +25695,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -25801,7 +25801,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -25836,7 +25836,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÔI TRƯỜNG QUANH EM</t>
+          <t>Chủ đề: Môi trường quanh em</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
